--- a/research/traditional_assets/database/data/zambia/zambia_tobacco.xlsx
+++ b/research/traditional_assets/database/data/zambia/zambia_tobacco.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1369198098774121</v>
+        <v>0.1364698405428412</v>
       </c>
       <c r="C2">
-        <v>30.87522585626014</v>
+        <v>30.62703340985896</v>
       </c>
       <c r="D2">
-        <v>25.45522585626014</v>
+        <v>25.51523340985896</v>
       </c>
       <c r="E2">
-        <v>-0.92</v>
+        <v>-0.6118</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.3082</v>
       </c>
       <c r="G2">
         <v>5.42</v>
@@ -1445,28 +1445,28 @@
         <v>8.09</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.01550246</v>
       </c>
       <c r="N2">
-        <v>8.09</v>
+        <v>8.074497539999999</v>
       </c>
       <c r="O2">
-        <v>2.8315</v>
+        <v>2.826074139</v>
       </c>
       <c r="P2">
-        <v>5.2585</v>
+        <v>5.248423401</v>
       </c>
       <c r="Q2">
-        <v>5.688499999999999</v>
+        <v>5.678423401</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1369198098774121</v>
+        <v>0.1375180712553952</v>
       </c>
       <c r="T2">
-        <v>0.5572774141861078</v>
+        <v>0.5609363062994509</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>521.8526608035111</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1364698405428412</v>
+        <v>0.1360198712082703</v>
       </c>
       <c r="C3">
-        <v>30.62703340985896</v>
+        <v>30.37912455278912</v>
       </c>
       <c r="D3">
-        <v>25.51523340985896</v>
+        <v>25.57552455278912</v>
       </c>
       <c r="E3">
-        <v>-0.6118</v>
+        <v>-0.3036</v>
       </c>
       <c r="F3">
-        <v>0.3082</v>
+        <v>0.6164000000000001</v>
       </c>
       <c r="G3">
         <v>5.42</v>
@@ -1527,28 +1527,28 @@
         <v>8.09</v>
       </c>
       <c r="M3">
-        <v>0.01550246</v>
+        <v>0.03100492</v>
       </c>
       <c r="N3">
-        <v>8.074497539999999</v>
+        <v>8.058995079999999</v>
       </c>
       <c r="O3">
-        <v>2.826074139</v>
+        <v>2.820648277999999</v>
       </c>
       <c r="P3">
-        <v>5.248423401</v>
+        <v>5.238346802</v>
       </c>
       <c r="Q3">
-        <v>5.678423401</v>
+        <v>5.668346801999999</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1375180712553952</v>
+        <v>0.1381285420492554</v>
       </c>
       <c r="T3">
-        <v>0.5609363062994509</v>
+        <v>0.5646698696804133</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>521.8526608035111</v>
+        <v>260.9263304017555</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1360198712082703</v>
+        <v>0.1355699018736993</v>
       </c>
       <c r="C4">
-        <v>30.37912455278912</v>
+        <v>30.13150130013181</v>
       </c>
       <c r="D4">
-        <v>25.57552455278912</v>
+        <v>25.63610130013181</v>
       </c>
       <c r="E4">
-        <v>-0.3036</v>
+        <v>0.004599999999999937</v>
       </c>
       <c r="F4">
-        <v>0.6164000000000001</v>
+        <v>0.9246</v>
       </c>
       <c r="G4">
         <v>5.42</v>
@@ -1609,28 +1609,28 @@
         <v>8.09</v>
       </c>
       <c r="M4">
-        <v>0.03100492</v>
+        <v>0.04650737999999999</v>
       </c>
       <c r="N4">
-        <v>8.058995079999999</v>
+        <v>8.04349262</v>
       </c>
       <c r="O4">
-        <v>2.820648277999999</v>
+        <v>2.815222417</v>
       </c>
       <c r="P4">
-        <v>5.238346802</v>
+        <v>5.228270203000001</v>
       </c>
       <c r="Q4">
-        <v>5.668346801999999</v>
+        <v>5.658270203000001</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1381285420492554</v>
+        <v>0.1387515998697931</v>
       </c>
       <c r="T4">
-        <v>0.5646698696804133</v>
+        <v>0.5684804137496429</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>260.9263304017555</v>
+        <v>173.9508869345038</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1355699018736993</v>
+        <v>0.1351199325391284</v>
       </c>
       <c r="C5">
-        <v>30.13150130013181</v>
+        <v>29.8841656861047</v>
       </c>
       <c r="D5">
-        <v>25.63610130013181</v>
+        <v>25.69696568610471</v>
       </c>
       <c r="E5">
-        <v>0.004599999999999937</v>
+        <v>0.3128000000000001</v>
       </c>
       <c r="F5">
-        <v>0.9246</v>
+        <v>1.2328</v>
       </c>
       <c r="G5">
         <v>5.42</v>
@@ -1691,28 +1691,28 @@
         <v>8.09</v>
       </c>
       <c r="M5">
-        <v>0.04650737999999999</v>
+        <v>0.06200984</v>
       </c>
       <c r="N5">
-        <v>8.04349262</v>
+        <v>8.02799016</v>
       </c>
       <c r="O5">
-        <v>2.815222417</v>
+        <v>2.809796556</v>
       </c>
       <c r="P5">
-        <v>5.228270203000001</v>
+        <v>5.218193604</v>
       </c>
       <c r="Q5">
-        <v>5.658270203000001</v>
+        <v>5.648193603999999</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1387515998697931</v>
+        <v>0.1393876380615921</v>
       </c>
       <c r="T5">
-        <v>0.5684804137496429</v>
+        <v>0.5723703441536482</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>173.9508869345038</v>
+        <v>130.4631652008778</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1351199325391284</v>
+        <v>0.1346699632045574</v>
       </c>
       <c r="C6">
-        <v>29.8841656861047</v>
+        <v>29.63711976428985</v>
       </c>
       <c r="D6">
-        <v>25.69696568610471</v>
+        <v>25.75811976428984</v>
       </c>
       <c r="E6">
-        <v>0.3128000000000001</v>
+        <v>0.6210000000000001</v>
       </c>
       <c r="F6">
-        <v>1.2328</v>
+        <v>1.541</v>
       </c>
       <c r="G6">
         <v>5.42</v>
@@ -1773,28 +1773,28 @@
         <v>8.09</v>
       </c>
       <c r="M6">
-        <v>0.06200984</v>
+        <v>0.07751230000000001</v>
       </c>
       <c r="N6">
-        <v>8.02799016</v>
+        <v>8.012487699999999</v>
       </c>
       <c r="O6">
-        <v>2.809796556</v>
+        <v>2.804370695</v>
       </c>
       <c r="P6">
-        <v>5.218193604</v>
+        <v>5.208117005</v>
       </c>
       <c r="Q6">
-        <v>5.648193603999999</v>
+        <v>5.638117005</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1393876380615921</v>
+        <v>0.1400370665311131</v>
       </c>
       <c r="T6">
-        <v>0.5723703441536482</v>
+        <v>0.5763421678293167</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>130.4631652008778</v>
+        <v>104.3705321607022</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1346699632045574</v>
+        <v>0.1342199938699865</v>
       </c>
       <c r="C7">
-        <v>29.63711976428985</v>
+        <v>29.3903656078644</v>
       </c>
       <c r="D7">
-        <v>25.75811976428984</v>
+        <v>25.8195656078644</v>
       </c>
       <c r="E7">
-        <v>0.6210000000000001</v>
+        <v>0.9292000000000001</v>
       </c>
       <c r="F7">
-        <v>1.541</v>
+        <v>1.8492</v>
       </c>
       <c r="G7">
         <v>5.42</v>
@@ -1855,28 +1855,28 @@
         <v>8.09</v>
       </c>
       <c r="M7">
-        <v>0.07751230000000001</v>
+        <v>0.09301476</v>
       </c>
       <c r="N7">
-        <v>8.012487699999999</v>
+        <v>7.99698524</v>
       </c>
       <c r="O7">
-        <v>2.804370695</v>
+        <v>2.798944834</v>
       </c>
       <c r="P7">
-        <v>5.208117005</v>
+        <v>5.198040406000001</v>
       </c>
       <c r="Q7">
-        <v>5.638117005</v>
+        <v>5.628040406</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1400370665311131</v>
+        <v>0.1407003126276452</v>
       </c>
       <c r="T7">
-        <v>0.5763421678293167</v>
+        <v>0.5803984983917017</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>104.3705321607022</v>
+        <v>86.97544346725186</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1342199938699865</v>
+        <v>0.1337700245354156</v>
       </c>
       <c r="C8">
-        <v>29.3903656078644</v>
+        <v>29.14390530983514</v>
       </c>
       <c r="D8">
-        <v>25.8195656078644</v>
+        <v>25.88130530983514</v>
       </c>
       <c r="E8">
-        <v>0.9291999999999999</v>
+        <v>1.2374</v>
       </c>
       <c r="F8">
-        <v>1.8492</v>
+        <v>2.1574</v>
       </c>
       <c r="G8">
         <v>5.42</v>
@@ -1937,28 +1937,28 @@
         <v>8.09</v>
       </c>
       <c r="M8">
-        <v>0.09301475999999999</v>
+        <v>0.10851722</v>
       </c>
       <c r="N8">
-        <v>7.99698524</v>
+        <v>7.981482779999999</v>
       </c>
       <c r="O8">
-        <v>2.798944834</v>
+        <v>2.793518973</v>
       </c>
       <c r="P8">
-        <v>5.198040406000001</v>
+        <v>5.187963806999999</v>
       </c>
       <c r="Q8">
-        <v>5.628040406</v>
+        <v>5.617963806999999</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1407003126276452</v>
+        <v>0.141377822081092</v>
       </c>
       <c r="T8">
-        <v>0.5803984983917017</v>
+        <v>0.5845420618694065</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>86.97544346725188</v>
+        <v>74.5503801147873</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1337700245354155</v>
+        <v>0.1333200552008446</v>
       </c>
       <c r="C9">
-        <v>29.14390530983514</v>
+        <v>28.89774098327593</v>
       </c>
       <c r="D9">
-        <v>25.88130530983515</v>
+        <v>25.94334098327593</v>
       </c>
       <c r="E9">
-        <v>1.2374</v>
+        <v>1.5456</v>
       </c>
       <c r="F9">
-        <v>2.1574</v>
+        <v>2.4656</v>
       </c>
       <c r="G9">
         <v>5.42</v>
@@ -2019,28 +2019,28 @@
         <v>8.09</v>
       </c>
       <c r="M9">
-        <v>0.10851722</v>
+        <v>0.12401968</v>
       </c>
       <c r="N9">
-        <v>7.981482779999999</v>
+        <v>7.96598032</v>
       </c>
       <c r="O9">
-        <v>2.793518973</v>
+        <v>2.788093112</v>
       </c>
       <c r="P9">
-        <v>5.187963806999999</v>
+        <v>5.177887208</v>
       </c>
       <c r="Q9">
-        <v>5.617963806999999</v>
+        <v>5.607887207999999</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.141377822081092</v>
+        <v>0.142070060000918</v>
       </c>
       <c r="T9">
-        <v>0.5845420618694065</v>
+        <v>0.5887757028140181</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>74.5503801147873</v>
+        <v>65.2315826004389</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1333200552008446</v>
+        <v>0.1328700858662737</v>
       </c>
       <c r="C10">
-        <v>28.89774098327593</v>
+        <v>28.65187476156892</v>
       </c>
       <c r="D10">
-        <v>25.94334098327593</v>
+        <v>26.00567476156892</v>
       </c>
       <c r="E10">
-        <v>1.5456</v>
+        <v>1.8538</v>
       </c>
       <c r="F10">
-        <v>2.4656</v>
+        <v>2.7738</v>
       </c>
       <c r="G10">
         <v>5.42</v>
@@ -2101,28 +2101,28 @@
         <v>8.09</v>
       </c>
       <c r="M10">
-        <v>0.12401968</v>
+        <v>0.13952214</v>
       </c>
       <c r="N10">
-        <v>7.96598032</v>
+        <v>7.950477859999999</v>
       </c>
       <c r="O10">
-        <v>2.788093112</v>
+        <v>2.782667250999999</v>
       </c>
       <c r="P10">
-        <v>5.177887208</v>
+        <v>5.167810609</v>
       </c>
       <c r="Q10">
-        <v>5.607887207999999</v>
+        <v>5.597810609</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.142070060000918</v>
+        <v>0.1427775119409601</v>
       </c>
       <c r="T10">
-        <v>0.5887757028140181</v>
+        <v>0.5931023908123575</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>65.2315826004389</v>
+        <v>57.98362897816791</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1328700858662737</v>
+        <v>0.1324201165317027</v>
       </c>
       <c r="C11">
-        <v>28.65187476156892</v>
+        <v>28.406308798649</v>
       </c>
       <c r="D11">
-        <v>26.00567476156892</v>
+        <v>26.068308798649</v>
       </c>
       <c r="E11">
-        <v>1.8538</v>
+        <v>2.162</v>
       </c>
       <c r="F11">
-        <v>2.7738</v>
+        <v>3.082</v>
       </c>
       <c r="G11">
         <v>5.42</v>
@@ -2183,28 +2183,28 @@
         <v>8.09</v>
       </c>
       <c r="M11">
-        <v>0.13952214</v>
+        <v>0.1550246</v>
       </c>
       <c r="N11">
-        <v>7.950477859999999</v>
+        <v>7.9349754</v>
       </c>
       <c r="O11">
-        <v>2.782667250999999</v>
+        <v>2.77724139</v>
       </c>
       <c r="P11">
-        <v>5.167810609</v>
+        <v>5.15773401</v>
       </c>
       <c r="Q11">
-        <v>5.597810609</v>
+        <v>5.58773401</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1427775119409601</v>
+        <v>0.1435006850352253</v>
       </c>
       <c r="T11">
-        <v>0.5931023908123575</v>
+        <v>0.5975252274328822</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>57.98362897816791</v>
+        <v>52.18526608035112</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1324201165317027</v>
+        <v>0.1319701471971318</v>
       </c>
       <c r="C12">
-        <v>28.406308798649</v>
+        <v>28.16104526925202</v>
       </c>
       <c r="D12">
-        <v>26.068308798649</v>
+        <v>26.13124526925202</v>
       </c>
       <c r="E12">
-        <v>2.162</v>
+        <v>2.4702</v>
       </c>
       <c r="F12">
-        <v>3.082</v>
+        <v>3.3902</v>
       </c>
       <c r="G12">
         <v>5.42</v>
@@ -2265,28 +2265,28 @@
         <v>8.09</v>
       </c>
       <c r="M12">
-        <v>0.1550246</v>
+        <v>0.17052706</v>
       </c>
       <c r="N12">
-        <v>7.9349754</v>
+        <v>7.919472939999999</v>
       </c>
       <c r="O12">
-        <v>2.77724139</v>
+        <v>2.771815529</v>
       </c>
       <c r="P12">
-        <v>5.15773401</v>
+        <v>5.147657411</v>
       </c>
       <c r="Q12">
-        <v>5.58773401</v>
+        <v>5.577657411</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1435006850352253</v>
+        <v>0.1442401092102605</v>
       </c>
       <c r="T12">
-        <v>0.5975252274328822</v>
+        <v>0.602047453640385</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>52.18526608035111</v>
+        <v>47.44115098213737</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1319701471971318</v>
+        <v>0.1315201778625608</v>
       </c>
       <c r="C13">
-        <v>28.16104526925202</v>
+        <v>27.91608636916641</v>
       </c>
       <c r="D13">
-        <v>26.13124526925202</v>
+        <v>26.19448636916641</v>
       </c>
       <c r="E13">
-        <v>2.4702</v>
+        <v>2.7784</v>
       </c>
       <c r="F13">
-        <v>3.3902</v>
+        <v>3.6984</v>
       </c>
       <c r="G13">
         <v>5.42</v>
@@ -2347,28 +2347,28 @@
         <v>8.09</v>
       </c>
       <c r="M13">
-        <v>0.17052706</v>
+        <v>0.18602952</v>
       </c>
       <c r="N13">
-        <v>7.919472939999999</v>
+        <v>7.90397048</v>
       </c>
       <c r="O13">
-        <v>2.771815529</v>
+        <v>2.766389668</v>
       </c>
       <c r="P13">
-        <v>5.147657411</v>
+        <v>5.137580811999999</v>
       </c>
       <c r="Q13">
-        <v>5.577657411</v>
+        <v>5.567580811999999</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1442401092102605</v>
+        <v>0.1449963384801828</v>
       </c>
       <c r="T13">
-        <v>0.602047453640385</v>
+        <v>0.60667245771624</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>47.44115098213737</v>
+        <v>43.48772173362594</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1315201778625608</v>
+        <v>0.1310702085279899</v>
       </c>
       <c r="C14">
-        <v>27.91608636916641</v>
+        <v>27.67143431548855</v>
       </c>
       <c r="D14">
-        <v>26.19448636916641</v>
+        <v>26.25803431548855</v>
       </c>
       <c r="E14">
-        <v>2.7784</v>
+        <v>3.086600000000001</v>
       </c>
       <c r="F14">
-        <v>3.6984</v>
+        <v>4.006600000000001</v>
       </c>
       <c r="G14">
         <v>5.42</v>
@@ -2429,28 +2429,28 @@
         <v>8.09</v>
       </c>
       <c r="M14">
-        <v>0.18602952</v>
+        <v>0.20153198</v>
       </c>
       <c r="N14">
-        <v>7.90397048</v>
+        <v>7.888468019999999</v>
       </c>
       <c r="O14">
-        <v>2.766389668</v>
+        <v>2.760963807</v>
       </c>
       <c r="P14">
-        <v>5.137580811999999</v>
+        <v>5.127504213</v>
       </c>
       <c r="Q14">
-        <v>5.567580811999999</v>
+        <v>5.557504213</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1449963384801828</v>
+        <v>0.1457699523310229</v>
       </c>
       <c r="T14">
-        <v>0.60667245771624</v>
+        <v>0.6114037837248734</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>43.48772173362594</v>
+        <v>40.14251236950085</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1310702085279899</v>
+        <v>0.130620239193419</v>
       </c>
       <c r="C15">
-        <v>27.67143431548855</v>
+        <v>27.4270913468819</v>
       </c>
       <c r="D15">
-        <v>26.25803431548855</v>
+        <v>26.3218913468819</v>
       </c>
       <c r="E15">
-        <v>3.086600000000001</v>
+        <v>3.394800000000001</v>
       </c>
       <c r="F15">
-        <v>4.006600000000001</v>
+        <v>4.314800000000001</v>
       </c>
       <c r="G15">
         <v>5.42</v>
@@ -2511,28 +2511,28 @@
         <v>8.09</v>
       </c>
       <c r="M15">
-        <v>0.20153198</v>
+        <v>0.21703444</v>
       </c>
       <c r="N15">
-        <v>7.888468019999999</v>
+        <v>7.87296556</v>
       </c>
       <c r="O15">
-        <v>2.760963807</v>
+        <v>2.755537946</v>
       </c>
       <c r="P15">
-        <v>5.127504213</v>
+        <v>5.117427614</v>
       </c>
       <c r="Q15">
-        <v>5.557504213</v>
+        <v>5.547427614</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1457699523310229</v>
+        <v>0.14656155720165</v>
       </c>
       <c r="T15">
-        <v>0.6114037837248734</v>
+        <v>0.6162451405709169</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>40.14251236950085</v>
+        <v>37.27519005739365</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.130620239193419</v>
+        <v>0.130170269858848</v>
       </c>
       <c r="C16">
-        <v>27.4270913468819</v>
+        <v>27.18305972383991</v>
       </c>
       <c r="D16">
-        <v>26.3218913468819</v>
+        <v>26.38605972383991</v>
       </c>
       <c r="E16">
-        <v>3.394800000000001</v>
+        <v>3.703000000000001</v>
       </c>
       <c r="F16">
-        <v>4.314800000000001</v>
+        <v>4.623000000000001</v>
       </c>
       <c r="G16">
         <v>5.42</v>
@@ -2593,28 +2593,28 @@
         <v>8.09</v>
       </c>
       <c r="M16">
-        <v>0.21703444</v>
+        <v>0.2325369</v>
       </c>
       <c r="N16">
-        <v>7.87296556</v>
+        <v>7.857463099999999</v>
       </c>
       <c r="O16">
-        <v>2.755537946</v>
+        <v>2.750112085</v>
       </c>
       <c r="P16">
-        <v>5.117427614</v>
+        <v>5.107351015</v>
       </c>
       <c r="Q16">
-        <v>5.547427614</v>
+        <v>5.537351015</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.14656155720165</v>
+        <v>0.147371788069233</v>
       </c>
       <c r="T16">
-        <v>0.6162451405709169</v>
+        <v>0.6212004116956907</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>37.27519005739365</v>
+        <v>34.79017738690074</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.130170269858848</v>
+        <v>0.1297203005242771</v>
       </c>
       <c r="C17">
-        <v>27.18305972383991</v>
+        <v>26.93934172895265</v>
       </c>
       <c r="D17">
-        <v>26.38605972383991</v>
+        <v>26.45054172895265</v>
       </c>
       <c r="E17">
-        <v>3.703</v>
+        <v>4.011200000000001</v>
       </c>
       <c r="F17">
-        <v>4.623</v>
+        <v>4.9312</v>
       </c>
       <c r="G17">
         <v>5.42</v>
@@ -2675,28 +2675,28 @@
         <v>8.09</v>
       </c>
       <c r="M17">
-        <v>0.2325369</v>
+        <v>0.24803936</v>
       </c>
       <c r="N17">
-        <v>7.857463099999999</v>
+        <v>7.84196064</v>
       </c>
       <c r="O17">
-        <v>2.750112085</v>
+        <v>2.744686224</v>
       </c>
       <c r="P17">
-        <v>5.107351015</v>
+        <v>5.097274416</v>
       </c>
       <c r="Q17">
-        <v>5.537351015</v>
+        <v>5.527274416</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.147371788069233</v>
+        <v>0.1482013101479489</v>
       </c>
       <c r="T17">
-        <v>0.6212004116956907</v>
+        <v>0.6262736654662926</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>34.79017738690074</v>
+        <v>32.61579130021944</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1297203005242771</v>
+        <v>0.1292703311897061</v>
       </c>
       <c r="C18">
-        <v>26.93934172895265</v>
+        <v>26.6959396671776</v>
       </c>
       <c r="D18">
-        <v>26.45054172895265</v>
+        <v>26.5153396671776</v>
       </c>
       <c r="E18">
-        <v>4.011200000000001</v>
+        <v>4.319400000000001</v>
       </c>
       <c r="F18">
-        <v>4.9312</v>
+        <v>5.239400000000001</v>
       </c>
       <c r="G18">
         <v>5.42</v>
@@ -2757,28 +2757,28 @@
         <v>8.09</v>
       </c>
       <c r="M18">
-        <v>0.24803936</v>
+        <v>0.26354182</v>
       </c>
       <c r="N18">
-        <v>7.84196064</v>
+        <v>7.826458179999999</v>
       </c>
       <c r="O18">
-        <v>2.744686224</v>
+        <v>2.739260363</v>
       </c>
       <c r="P18">
-        <v>5.097274416</v>
+        <v>5.087197817</v>
       </c>
       <c r="Q18">
-        <v>5.527274416</v>
+        <v>5.517197817</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1482013101479489</v>
+        <v>0.1490508207104893</v>
       </c>
       <c r="T18">
-        <v>0.6262736654662926</v>
+        <v>0.631469166315704</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>32.61579130021944</v>
+        <v>30.697215341383</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1292703311897061</v>
+        <v>0.1288203618551352</v>
       </c>
       <c r="C19">
-        <v>26.6959396671776</v>
+        <v>26.45285586611419</v>
       </c>
       <c r="D19">
-        <v>26.5153396671776</v>
+        <v>26.5804558661142</v>
       </c>
       <c r="E19">
-        <v>4.319400000000001</v>
+        <v>4.627600000000001</v>
       </c>
       <c r="F19">
-        <v>5.239400000000001</v>
+        <v>5.547600000000001</v>
       </c>
       <c r="G19">
         <v>5.42</v>
@@ -2839,28 +2839,28 @@
         <v>8.09</v>
       </c>
       <c r="M19">
-        <v>0.26354182</v>
+        <v>0.27904428</v>
       </c>
       <c r="N19">
-        <v>7.826458179999999</v>
+        <v>7.81095572</v>
       </c>
       <c r="O19">
-        <v>2.739260363</v>
+        <v>2.733834502</v>
       </c>
       <c r="P19">
-        <v>5.087197817</v>
+        <v>5.077121218</v>
       </c>
       <c r="Q19">
-        <v>5.517197817</v>
+        <v>5.507121218</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1490508207104893</v>
+        <v>0.1499210510428478</v>
       </c>
       <c r="T19">
-        <v>0.631469166315704</v>
+        <v>0.6367913866980279</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>30.697215341383</v>
+        <v>28.99181448908395</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1288203618551352</v>
+        <v>0.1283703925205643</v>
       </c>
       <c r="C20">
-        <v>26.4528558661142</v>
+        <v>26.21009267628261</v>
       </c>
       <c r="D20">
-        <v>26.5804558661142</v>
+        <v>26.64589267628261</v>
       </c>
       <c r="E20">
-        <v>4.6276</v>
+        <v>4.9358</v>
       </c>
       <c r="F20">
-        <v>5.5476</v>
+        <v>5.8558</v>
       </c>
       <c r="G20">
         <v>5.42</v>
@@ -2921,28 +2921,28 @@
         <v>8.09</v>
       </c>
       <c r="M20">
-        <v>0.27904428</v>
+        <v>0.29454674</v>
       </c>
       <c r="N20">
-        <v>7.81095572</v>
+        <v>7.795453259999999</v>
       </c>
       <c r="O20">
-        <v>2.733834502</v>
+        <v>2.728408641</v>
       </c>
       <c r="P20">
-        <v>5.077121218</v>
+        <v>5.067044619</v>
       </c>
       <c r="Q20">
-        <v>5.507121218</v>
+        <v>5.497044619</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1499210510428478</v>
+        <v>0.1508127685439065</v>
       </c>
       <c r="T20">
-        <v>0.6367913866980279</v>
+        <v>0.6422450199292983</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>28.99181448908396</v>
+        <v>27.46592951597427</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1283703925205643</v>
+        <v>0.1279204231859933</v>
       </c>
       <c r="C21">
-        <v>26.21009267628261</v>
+        <v>25.96765247140653</v>
       </c>
       <c r="D21">
-        <v>26.64589267628261</v>
+        <v>26.71165247140653</v>
       </c>
       <c r="E21">
-        <v>4.9358</v>
+        <v>5.244000000000001</v>
       </c>
       <c r="F21">
-        <v>5.8558</v>
+        <v>6.164000000000001</v>
       </c>
       <c r="G21">
         <v>5.42</v>
@@ -3003,28 +3003,28 @@
         <v>8.09</v>
       </c>
       <c r="M21">
-        <v>0.29454674</v>
+        <v>0.3100492</v>
       </c>
       <c r="N21">
-        <v>7.795453259999999</v>
+        <v>7.7799508</v>
       </c>
       <c r="O21">
-        <v>2.728408641</v>
+        <v>2.72298278</v>
       </c>
       <c r="P21">
-        <v>5.067044619</v>
+        <v>5.05696802</v>
       </c>
       <c r="Q21">
-        <v>5.497044619</v>
+        <v>5.48696802</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1508127685439065</v>
+        <v>0.1517267789824917</v>
       </c>
       <c r="T21">
-        <v>0.6422450199292983</v>
+        <v>0.6478349939913504</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>27.46592951597427</v>
+        <v>26.09263304017556</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1279204231859933</v>
+        <v>0.1274704538514224</v>
       </c>
       <c r="C22">
-        <v>25.96765247140653</v>
+        <v>25.72553764870022</v>
       </c>
       <c r="D22">
-        <v>26.71165247140653</v>
+        <v>26.77773764870022</v>
       </c>
       <c r="E22">
-        <v>5.244000000000001</v>
+        <v>5.552200000000001</v>
       </c>
       <c r="F22">
-        <v>6.164000000000001</v>
+        <v>6.472200000000001</v>
       </c>
       <c r="G22">
         <v>5.42</v>
@@ -3085,28 +3085,28 @@
         <v>8.09</v>
       </c>
       <c r="M22">
-        <v>0.3100492</v>
+        <v>0.32555166</v>
       </c>
       <c r="N22">
-        <v>7.7799508</v>
+        <v>7.76444834</v>
       </c>
       <c r="O22">
-        <v>2.72298278</v>
+        <v>2.717556919</v>
       </c>
       <c r="P22">
-        <v>5.05696802</v>
+        <v>5.046891421</v>
       </c>
       <c r="Q22">
-        <v>5.48696802</v>
+        <v>5.476891420999999</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1517267789824917</v>
+        <v>0.1526639289258511</v>
       </c>
       <c r="T22">
-        <v>0.6478349939913504</v>
+        <v>0.6535664863840872</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>26.09263304017556</v>
+        <v>24.8501267049291</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1274704538514224</v>
+        <v>0.1270204845168514</v>
       </c>
       <c r="C23">
-        <v>25.72553764870022</v>
+        <v>25.48375062915979</v>
       </c>
       <c r="D23">
-        <v>26.77773764870022</v>
+        <v>26.84415062915978</v>
       </c>
       <c r="E23">
-        <v>5.5522</v>
+        <v>5.8604</v>
       </c>
       <c r="F23">
-        <v>6.4722</v>
+        <v>6.7804</v>
       </c>
       <c r="G23">
         <v>5.42</v>
@@ -3167,28 +3167,28 @@
         <v>8.09</v>
       </c>
       <c r="M23">
-        <v>0.32555166</v>
+        <v>0.34105412</v>
       </c>
       <c r="N23">
-        <v>7.76444834</v>
+        <v>7.74894588</v>
       </c>
       <c r="O23">
-        <v>2.717556919</v>
+        <v>2.712131058</v>
       </c>
       <c r="P23">
-        <v>5.046891421</v>
+        <v>5.036814822</v>
       </c>
       <c r="Q23">
-        <v>5.476891420999999</v>
+        <v>5.466814822</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1526639289258511</v>
+        <v>0.1536251083549377</v>
       </c>
       <c r="T23">
-        <v>0.6535664863840872</v>
+        <v>0.6594449401202276</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>24.85012670492911</v>
+        <v>23.72057549106869</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1270204845168514</v>
+        <v>0.1265705151822805</v>
       </c>
       <c r="C24">
-        <v>25.48375062915979</v>
+        <v>25.24229385785888</v>
       </c>
       <c r="D24">
-        <v>26.84415062915978</v>
+        <v>26.91089385785888</v>
       </c>
       <c r="E24">
-        <v>5.8604</v>
+        <v>6.168600000000001</v>
       </c>
       <c r="F24">
-        <v>6.7804</v>
+        <v>7.0886</v>
       </c>
       <c r="G24">
         <v>5.42</v>
@@ -3249,28 +3249,28 @@
         <v>8.09</v>
       </c>
       <c r="M24">
-        <v>0.34105412</v>
+        <v>0.35655658</v>
       </c>
       <c r="N24">
-        <v>7.74894588</v>
+        <v>7.73344342</v>
       </c>
       <c r="O24">
-        <v>2.712131058</v>
+        <v>2.706705197</v>
       </c>
       <c r="P24">
-        <v>5.036814822</v>
+        <v>5.026738223</v>
       </c>
       <c r="Q24">
-        <v>5.466814822</v>
+        <v>5.456738222999999</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1536251083549377</v>
+        <v>0.1546112534834811</v>
       </c>
       <c r="T24">
-        <v>0.6594449401202276</v>
+        <v>0.6654760809663975</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>23.72057549106869</v>
+        <v>22.68924612189179</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1265705151822805</v>
+        <v>0.1261205458477095</v>
       </c>
       <c r="C25">
-        <v>25.24229385785888</v>
+        <v>25.00116980424872</v>
       </c>
       <c r="D25">
-        <v>26.91089385785888</v>
+        <v>26.97796980424872</v>
       </c>
       <c r="E25">
-        <v>6.168600000000001</v>
+        <v>6.476800000000001</v>
       </c>
       <c r="F25">
-        <v>7.0886</v>
+        <v>7.396800000000001</v>
       </c>
       <c r="G25">
         <v>5.42</v>
@@ -3331,28 +3331,28 @@
         <v>8.09</v>
       </c>
       <c r="M25">
-        <v>0.35655658</v>
+        <v>0.37205904</v>
       </c>
       <c r="N25">
-        <v>7.73344342</v>
+        <v>7.71794096</v>
       </c>
       <c r="O25">
-        <v>2.706705197</v>
+        <v>2.701279336</v>
       </c>
       <c r="P25">
-        <v>5.026738223</v>
+        <v>5.016661624</v>
       </c>
       <c r="Q25">
-        <v>5.456738222999999</v>
+        <v>5.446661624</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1546112534834811</v>
+        <v>0.1556233497996178</v>
       </c>
       <c r="T25">
-        <v>0.6654760809663975</v>
+        <v>0.6716659360453614</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>22.68924612189179</v>
+        <v>21.74386086681297</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1261205458477095</v>
+        <v>0.1256705765131386</v>
       </c>
       <c r="C26">
-        <v>25.00116980424872</v>
+        <v>24.76038096246267</v>
       </c>
       <c r="D26">
-        <v>26.97796980424872</v>
+        <v>27.04538096246267</v>
       </c>
       <c r="E26">
-        <v>6.4768</v>
+        <v>6.785</v>
       </c>
       <c r="F26">
-        <v>7.3968</v>
+        <v>7.705</v>
       </c>
       <c r="G26">
         <v>5.42</v>
@@ -3413,28 +3413,28 @@
         <v>8.09</v>
       </c>
       <c r="M26">
-        <v>0.37205904</v>
+        <v>0.3875615</v>
       </c>
       <c r="N26">
-        <v>7.71794096</v>
+        <v>7.7024385</v>
       </c>
       <c r="O26">
-        <v>2.701279336</v>
+        <v>2.695853475</v>
       </c>
       <c r="P26">
-        <v>5.016661624</v>
+        <v>5.006585025</v>
       </c>
       <c r="Q26">
-        <v>5.446661624</v>
+        <v>5.436585024999999</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1556233497996178</v>
+        <v>0.1566624353508515</v>
       </c>
       <c r="T26">
-        <v>0.6716659360453614</v>
+        <v>0.6780208539264312</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>21.74386086681297</v>
+        <v>20.87410643214045</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1256705765131386</v>
+        <v>0.1252206071785676</v>
       </c>
       <c r="C27">
-        <v>24.76038096246267</v>
+        <v>24.51992985162539</v>
       </c>
       <c r="D27">
-        <v>27.04538096246267</v>
+        <v>27.11312985162539</v>
       </c>
       <c r="E27">
-        <v>6.785</v>
+        <v>7.093200000000001</v>
       </c>
       <c r="F27">
-        <v>7.705</v>
+        <v>8.013200000000001</v>
       </c>
       <c r="G27">
         <v>5.42</v>
@@ -3495,28 +3495,28 @@
         <v>8.09</v>
       </c>
       <c r="M27">
-        <v>0.3875615</v>
+        <v>0.4030639600000001</v>
       </c>
       <c r="N27">
-        <v>7.7024385</v>
+        <v>7.68693604</v>
       </c>
       <c r="O27">
-        <v>2.695853475</v>
+        <v>2.690427614</v>
       </c>
       <c r="P27">
-        <v>5.006585025</v>
+        <v>4.996508426</v>
       </c>
       <c r="Q27">
-        <v>5.436585024999999</v>
+        <v>5.426508426</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1566624353508515</v>
+        <v>0.1577296042953617</v>
       </c>
       <c r="T27">
-        <v>0.6780208539264312</v>
+        <v>0.684547526344827</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>20.87410643214045</v>
+        <v>20.07125618475043</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1252206071785676</v>
+        <v>0.1247706378439967</v>
       </c>
       <c r="C28">
-        <v>24.51992985162539</v>
+        <v>24.27981901616664</v>
       </c>
       <c r="D28">
-        <v>27.11312985162539</v>
+        <v>27.18121901616664</v>
       </c>
       <c r="E28">
-        <v>7.093200000000001</v>
+        <v>7.401400000000001</v>
       </c>
       <c r="F28">
-        <v>8.013200000000001</v>
+        <v>8.321400000000001</v>
       </c>
       <c r="G28">
         <v>5.42</v>
@@ -3577,28 +3577,28 @@
         <v>8.09</v>
       </c>
       <c r="M28">
-        <v>0.4030639600000001</v>
+        <v>0.41856642</v>
       </c>
       <c r="N28">
-        <v>7.68693604</v>
+        <v>7.67143358</v>
       </c>
       <c r="O28">
-        <v>2.690427614</v>
+        <v>2.685001753</v>
       </c>
       <c r="P28">
-        <v>4.996508426</v>
+        <v>4.986431827</v>
       </c>
       <c r="Q28">
-        <v>5.426508426</v>
+        <v>5.416431826999999</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1577296042953617</v>
+        <v>0.158826010745201</v>
       </c>
       <c r="T28">
-        <v>0.684547526344827</v>
+        <v>0.6912530117061926</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>20.07125618475043</v>
+        <v>19.32787632605597</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1247706378439967</v>
+        <v>0.1243206685094258</v>
       </c>
       <c r="C29">
-        <v>24.27981901616664</v>
+        <v>24.04005102613981</v>
       </c>
       <c r="D29">
-        <v>27.18121901616664</v>
+        <v>27.24965102613982</v>
       </c>
       <c r="E29">
-        <v>7.401400000000001</v>
+        <v>7.709600000000002</v>
       </c>
       <c r="F29">
-        <v>8.321400000000001</v>
+        <v>8.629600000000002</v>
       </c>
       <c r="G29">
         <v>5.42</v>
@@ -3659,28 +3659,28 @@
         <v>8.09</v>
       </c>
       <c r="M29">
-        <v>0.41856642</v>
+        <v>0.43406888</v>
       </c>
       <c r="N29">
-        <v>7.67143358</v>
+        <v>7.65593112</v>
       </c>
       <c r="O29">
-        <v>2.685001753</v>
+        <v>2.679575892</v>
       </c>
       <c r="P29">
-        <v>4.986431827</v>
+        <v>4.976355228</v>
       </c>
       <c r="Q29">
-        <v>5.416431826999999</v>
+        <v>5.406355228</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.158826010745201</v>
+        <v>0.159952872929758</v>
       </c>
       <c r="T29">
-        <v>0.6912530117061926</v>
+        <v>0.6981447605498183</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>19.32787632605597</v>
+        <v>18.63759502869683</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1243206685094258</v>
+        <v>0.1238706991748548</v>
       </c>
       <c r="C30">
-        <v>24.04005102613981</v>
+        <v>23.80062847754532</v>
       </c>
       <c r="D30">
-        <v>27.24965102613982</v>
+        <v>27.31842847754532</v>
       </c>
       <c r="E30">
-        <v>7.709600000000002</v>
+        <v>8.017800000000001</v>
       </c>
       <c r="F30">
-        <v>8.629600000000002</v>
+        <v>8.937800000000001</v>
       </c>
       <c r="G30">
         <v>5.42</v>
@@ -3741,28 +3741,28 @@
         <v>8.09</v>
       </c>
       <c r="M30">
-        <v>0.43406888</v>
+        <v>0.44957134</v>
       </c>
       <c r="N30">
-        <v>7.65593112</v>
+        <v>7.64042866</v>
       </c>
       <c r="O30">
-        <v>2.679575892</v>
+        <v>2.674150030999999</v>
       </c>
       <c r="P30">
-        <v>4.976355228</v>
+        <v>4.966278629</v>
       </c>
       <c r="Q30">
-        <v>5.406355228</v>
+        <v>5.396278628999999</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.159952872929758</v>
+        <v>0.1611114777110631</v>
       </c>
       <c r="T30">
-        <v>0.6981447605498183</v>
+        <v>0.7052306431636871</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>18.63759502869683</v>
+        <v>17.99491933805211</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1238706991748548</v>
+        <v>0.1234207298402839</v>
       </c>
       <c r="C31">
-        <v>23.80062847754533</v>
+        <v>23.56155399265886</v>
       </c>
       <c r="D31">
-        <v>27.31842847754532</v>
+        <v>27.38755399265886</v>
       </c>
       <c r="E31">
-        <v>8.017799999999999</v>
+        <v>8.326000000000001</v>
       </c>
       <c r="F31">
-        <v>8.937799999999999</v>
+        <v>9.246</v>
       </c>
       <c r="G31">
         <v>5.42</v>
@@ -3823,28 +3823,28 @@
         <v>8.09</v>
       </c>
       <c r="M31">
-        <v>0.4495713399999999</v>
+        <v>0.4650738</v>
       </c>
       <c r="N31">
-        <v>7.64042866</v>
+        <v>7.6249262</v>
       </c>
       <c r="O31">
-        <v>2.674150030999999</v>
+        <v>2.66872417</v>
       </c>
       <c r="P31">
-        <v>4.966278629</v>
+        <v>4.95620203</v>
       </c>
       <c r="Q31">
-        <v>5.396278628999999</v>
+        <v>5.38620203</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1611114777110631</v>
+        <v>0.1623031854861198</v>
       </c>
       <c r="T31">
-        <v>0.7052306431636871</v>
+        <v>0.7125189795665234</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>17.99491933805211</v>
+        <v>17.39508869345037</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1234207298402839</v>
+        <v>0.1229707605057129</v>
       </c>
       <c r="C32">
-        <v>23.56155399265886</v>
+        <v>23.32283022036465</v>
       </c>
       <c r="D32">
-        <v>27.38755399265886</v>
+        <v>27.45703022036465</v>
       </c>
       <c r="E32">
-        <v>8.326000000000001</v>
+        <v>8.6342</v>
       </c>
       <c r="F32">
-        <v>9.246</v>
+        <v>9.5542</v>
       </c>
       <c r="G32">
         <v>5.42</v>
@@ -3905,28 +3905,28 @@
         <v>8.09</v>
       </c>
       <c r="M32">
-        <v>0.4650738</v>
+        <v>0.48057626</v>
       </c>
       <c r="N32">
-        <v>7.6249262</v>
+        <v>7.60942374</v>
       </c>
       <c r="O32">
-        <v>2.66872417</v>
+        <v>2.663298309</v>
       </c>
       <c r="P32">
-        <v>4.95620203</v>
+        <v>4.946125431</v>
       </c>
       <c r="Q32">
-        <v>5.38620203</v>
+        <v>5.376125431</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1623031854861198</v>
+        <v>0.163529435515526</v>
       </c>
       <c r="T32">
-        <v>0.7125189795665234</v>
+        <v>0.7200185720969784</v>
       </c>
       <c r="U32">
         <v>0.0503</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>17.39508869345037</v>
+        <v>16.83395680011326</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1229707605057129</v>
+        <v>0.122520791171142</v>
       </c>
       <c r="C33">
-        <v>23.32283022036465</v>
+        <v>23.08445983649388</v>
       </c>
       <c r="D33">
-        <v>27.45703022036465</v>
+        <v>27.52685983649388</v>
       </c>
       <c r="E33">
-        <v>8.6342</v>
+        <v>8.942400000000001</v>
       </c>
       <c r="F33">
-        <v>9.5542</v>
+        <v>9.862400000000001</v>
       </c>
       <c r="G33">
         <v>5.42</v>
@@ -3987,28 +3987,28 @@
         <v>8.09</v>
       </c>
       <c r="M33">
-        <v>0.48057626</v>
+        <v>0.49607872</v>
       </c>
       <c r="N33">
-        <v>7.60942374</v>
+        <v>7.59392128</v>
       </c>
       <c r="O33">
-        <v>2.663298309</v>
+        <v>2.657872448</v>
       </c>
       <c r="P33">
-        <v>4.946125431</v>
+        <v>4.936048832</v>
       </c>
       <c r="Q33">
-        <v>5.376125431</v>
+        <v>5.366048832</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.163529435515526</v>
+        <v>0.1647917517222676</v>
       </c>
       <c r="T33">
-        <v>0.7200185720969784</v>
+        <v>0.727738740878329</v>
       </c>
       <c r="U33">
         <v>0.0503</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>16.83395680011326</v>
+        <v>16.30789565010972</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.122520791171142</v>
+        <v>0.1220708218365711</v>
       </c>
       <c r="C34">
-        <v>23.08445983649388</v>
+        <v>22.84644554416814</v>
       </c>
       <c r="D34">
-        <v>27.52685983649388</v>
+        <v>27.59704554416814</v>
       </c>
       <c r="E34">
-        <v>8.942400000000001</v>
+        <v>9.2506</v>
       </c>
       <c r="F34">
-        <v>9.862400000000001</v>
+        <v>10.1706</v>
       </c>
       <c r="G34">
         <v>5.42</v>
@@ -4069,28 +4069,28 @@
         <v>8.09</v>
       </c>
       <c r="M34">
-        <v>0.49607872</v>
+        <v>0.51158118</v>
       </c>
       <c r="N34">
-        <v>7.59392128</v>
+        <v>7.57841882</v>
       </c>
       <c r="O34">
-        <v>2.657872448</v>
+        <v>2.652446587</v>
       </c>
       <c r="P34">
-        <v>4.936048832</v>
+        <v>4.925972233</v>
       </c>
       <c r="Q34">
-        <v>5.366048832</v>
+        <v>5.355972232999999</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1647917517222676</v>
+        <v>0.1660917490098076</v>
       </c>
       <c r="T34">
-        <v>0.727738740878329</v>
+        <v>0.7356893624591229</v>
       </c>
       <c r="U34">
         <v>0.0503</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>16.30789565010972</v>
+        <v>15.81371699404579</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1220708218365711</v>
+        <v>0.1216208525020001</v>
       </c>
       <c r="C35">
-        <v>22.84644554416814</v>
+        <v>22.60879007414832</v>
       </c>
       <c r="D35">
-        <v>27.59704554416814</v>
+        <v>27.66759007414832</v>
       </c>
       <c r="E35">
-        <v>9.2506</v>
+        <v>9.558800000000002</v>
       </c>
       <c r="F35">
-        <v>10.1706</v>
+        <v>10.4788</v>
       </c>
       <c r="G35">
         <v>5.42</v>
@@ -4151,28 +4151,28 @@
         <v>8.09</v>
       </c>
       <c r="M35">
-        <v>0.51158118</v>
+        <v>0.5270836400000001</v>
       </c>
       <c r="N35">
-        <v>7.57841882</v>
+        <v>7.56291636</v>
       </c>
       <c r="O35">
-        <v>2.652446587</v>
+        <v>2.647020726</v>
       </c>
       <c r="P35">
-        <v>4.925972233</v>
+        <v>4.915895634</v>
       </c>
       <c r="Q35">
-        <v>5.355972232999999</v>
+        <v>5.345895634</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1660917490098076</v>
+        <v>0.1674311401545456</v>
       </c>
       <c r="T35">
-        <v>0.7356893624591229</v>
+        <v>0.7438809119666075</v>
       </c>
       <c r="U35">
         <v>0.0503</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>15.81371699404579</v>
+        <v>15.3486076706915</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1216208525020001</v>
+        <v>0.1211708831674291</v>
       </c>
       <c r="C36">
-        <v>22.60879007414832</v>
+        <v>22.3714961851887</v>
       </c>
       <c r="D36">
-        <v>27.66759007414832</v>
+        <v>27.7384961851887</v>
       </c>
       <c r="E36">
-        <v>9.558800000000002</v>
+        <v>9.867000000000001</v>
       </c>
       <c r="F36">
-        <v>10.4788</v>
+        <v>10.787</v>
       </c>
       <c r="G36">
         <v>5.42</v>
@@ -4233,28 +4233,28 @@
         <v>8.09</v>
       </c>
       <c r="M36">
-        <v>0.5270836400000001</v>
+        <v>0.5425861</v>
       </c>
       <c r="N36">
-        <v>7.56291636</v>
+        <v>7.5474139</v>
       </c>
       <c r="O36">
-        <v>2.647020726</v>
+        <v>2.641594865</v>
       </c>
       <c r="P36">
-        <v>4.915895634</v>
+        <v>4.905819035</v>
       </c>
       <c r="Q36">
-        <v>5.345895634</v>
+        <v>5.335819035</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1674311401545456</v>
+        <v>0.1688117433345064</v>
       </c>
       <c r="T36">
-        <v>0.7438809119666075</v>
+        <v>0.7523245091512455</v>
       </c>
       <c r="U36">
         <v>0.0503</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>15.3486076706915</v>
+        <v>14.91007602295746</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1211708831674291</v>
+        <v>0.1207209138328582</v>
       </c>
       <c r="C37">
-        <v>22.3714961851887</v>
+        <v>22.1345666643966</v>
       </c>
       <c r="D37">
-        <v>27.7384961851887</v>
+        <v>27.80976666439661</v>
       </c>
       <c r="E37">
-        <v>9.867000000000001</v>
+        <v>10.1752</v>
       </c>
       <c r="F37">
-        <v>10.787</v>
+        <v>11.0952</v>
       </c>
       <c r="G37">
         <v>5.42</v>
@@ -4315,28 +4315,28 @@
         <v>8.09</v>
       </c>
       <c r="M37">
-        <v>0.5425861</v>
+        <v>0.5580885600000001</v>
       </c>
       <c r="N37">
-        <v>7.5474139</v>
+        <v>7.53191144</v>
       </c>
       <c r="O37">
-        <v>2.641594865</v>
+        <v>2.636169004</v>
       </c>
       <c r="P37">
-        <v>4.905819035</v>
+        <v>4.895742436000001</v>
       </c>
       <c r="Q37">
-        <v>5.335819035</v>
+        <v>5.325742436000001</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1688117433345064</v>
+        <v>0.170235490363841</v>
       </c>
       <c r="T37">
-        <v>0.7523245091512455</v>
+        <v>0.7610319687479035</v>
       </c>
       <c r="U37">
         <v>0.0503</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>14.91007602295746</v>
+        <v>14.49590724454197</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1207209138328582</v>
+        <v>0.1202709444982873</v>
       </c>
       <c r="C38">
-        <v>22.1345666643966</v>
+        <v>21.89800432759763</v>
       </c>
       <c r="D38">
-        <v>27.8097666643966</v>
+        <v>27.88140432759762</v>
       </c>
       <c r="E38">
-        <v>10.1752</v>
+        <v>10.4834</v>
       </c>
       <c r="F38">
-        <v>11.0952</v>
+        <v>11.4034</v>
       </c>
       <c r="G38">
         <v>5.42</v>
@@ -4397,28 +4397,28 @@
         <v>8.09</v>
       </c>
       <c r="M38">
-        <v>0.55808856</v>
+        <v>0.57359102</v>
       </c>
       <c r="N38">
-        <v>7.53191144</v>
+        <v>7.51640898</v>
       </c>
       <c r="O38">
-        <v>2.636169004</v>
+        <v>2.630743143</v>
       </c>
       <c r="P38">
-        <v>4.895742436000001</v>
+        <v>4.885665836999999</v>
       </c>
       <c r="Q38">
-        <v>5.325742436000001</v>
+        <v>5.315665836999999</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.170235490363841</v>
+        <v>0.1717044357115671</v>
       </c>
       <c r="T38">
-        <v>0.7610319687479035</v>
+        <v>0.7700158556333442</v>
       </c>
       <c r="U38">
         <v>0.0503</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>14.49590724454198</v>
+        <v>14.10412596766247</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1202709444982873</v>
+        <v>0.1198209751637163</v>
       </c>
       <c r="C39">
-        <v>21.89800432759763</v>
+        <v>21.66181201970641</v>
       </c>
       <c r="D39">
-        <v>27.88140432759762</v>
+        <v>27.95341201970641</v>
       </c>
       <c r="E39">
-        <v>10.4834</v>
+        <v>10.7916</v>
       </c>
       <c r="F39">
-        <v>11.4034</v>
+        <v>11.7116</v>
       </c>
       <c r="G39">
         <v>5.42</v>
@@ -4479,28 +4479,28 @@
         <v>8.09</v>
       </c>
       <c r="M39">
-        <v>0.57359102</v>
+        <v>0.5890934800000001</v>
       </c>
       <c r="N39">
-        <v>7.51640898</v>
+        <v>7.50090652</v>
       </c>
       <c r="O39">
-        <v>2.630743143</v>
+        <v>2.625317282</v>
       </c>
       <c r="P39">
-        <v>4.885665836999999</v>
+        <v>4.875589238</v>
       </c>
       <c r="Q39">
-        <v>5.315665836999999</v>
+        <v>5.305589238</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1717044357115671</v>
+        <v>0.1732207663930909</v>
       </c>
       <c r="T39">
-        <v>0.7700158556333442</v>
+        <v>0.779289545321541</v>
       </c>
       <c r="U39">
         <v>0.0503</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>14.10412596766247</v>
+        <v>13.73296475798714</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1198209751637163</v>
+        <v>0.1193710058291454</v>
       </c>
       <c r="C40">
-        <v>21.66181201970641</v>
+        <v>21.42599261510331</v>
       </c>
       <c r="D40">
-        <v>27.95341201970641</v>
+        <v>28.02579261510331</v>
       </c>
       <c r="E40">
-        <v>10.7916</v>
+        <v>11.0998</v>
       </c>
       <c r="F40">
-        <v>11.7116</v>
+        <v>12.0198</v>
       </c>
       <c r="G40">
         <v>5.42</v>
@@ -4561,28 +4561,28 @@
         <v>8.09</v>
       </c>
       <c r="M40">
-        <v>0.5890934800000001</v>
+        <v>0.6045959399999999</v>
       </c>
       <c r="N40">
-        <v>7.50090652</v>
+        <v>7.48540406</v>
       </c>
       <c r="O40">
-        <v>2.625317282</v>
+        <v>2.619891421</v>
       </c>
       <c r="P40">
-        <v>4.875589238</v>
+        <v>4.865512639</v>
       </c>
       <c r="Q40">
-        <v>5.305589238</v>
+        <v>5.295512639</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1732207663930909</v>
+        <v>0.1747868128346646</v>
       </c>
       <c r="T40">
-        <v>0.779289545321541</v>
+        <v>0.788867290409351</v>
       </c>
       <c r="U40">
         <v>0.0503</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>13.73296475798714</v>
+        <v>13.38083745650029</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1193710058291454</v>
+        <v>0.1189210364945745</v>
       </c>
       <c r="C41">
-        <v>21.42599261510331</v>
+        <v>21.1905490180168</v>
       </c>
       <c r="D41">
-        <v>28.02579261510331</v>
+        <v>28.09854901801681</v>
       </c>
       <c r="E41">
-        <v>11.0998</v>
+        <v>11.408</v>
       </c>
       <c r="F41">
-        <v>12.0198</v>
+        <v>12.328</v>
       </c>
       <c r="G41">
         <v>5.42</v>
@@ -4643,28 +4643,28 @@
         <v>8.09</v>
       </c>
       <c r="M41">
-        <v>0.6045959399999999</v>
+        <v>0.6200984</v>
       </c>
       <c r="N41">
-        <v>7.48540406</v>
+        <v>7.4699016</v>
       </c>
       <c r="O41">
-        <v>2.619891421</v>
+        <v>2.61446556</v>
       </c>
       <c r="P41">
-        <v>4.865512639</v>
+        <v>4.855436040000001</v>
       </c>
       <c r="Q41">
-        <v>5.295512639</v>
+        <v>5.28543604</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1747868128346646</v>
+        <v>0.1764050608242908</v>
       </c>
       <c r="T41">
-        <v>0.788867290409351</v>
+        <v>0.7987642936667545</v>
       </c>
       <c r="U41">
         <v>0.0503</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>13.38083745650029</v>
+        <v>13.04631652008778</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1189210364945745</v>
+        <v>0.1188708171600035</v>
       </c>
       <c r="C42">
-        <v>21.1905490180168</v>
+        <v>20.89049251789393</v>
       </c>
       <c r="D42">
-        <v>28.09854901801681</v>
+        <v>28.10669251789394</v>
       </c>
       <c r="E42">
-        <v>11.408</v>
+        <v>11.7162</v>
       </c>
       <c r="F42">
-        <v>12.328</v>
+        <v>12.6362</v>
       </c>
       <c r="G42">
         <v>5.42</v>
@@ -4725,45 +4725,45 @@
         <v>8.09</v>
       </c>
       <c r="M42">
-        <v>0.6200984</v>
+        <v>0.65455516</v>
       </c>
       <c r="N42">
-        <v>7.4699016</v>
+        <v>7.43544484</v>
       </c>
       <c r="O42">
-        <v>2.61446556</v>
+        <v>2.602405694</v>
       </c>
       <c r="P42">
-        <v>4.855436040000001</v>
+        <v>4.833039146</v>
       </c>
       <c r="Q42">
-        <v>5.28543604</v>
+        <v>5.263039146</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1764050608242908</v>
+        <v>0.1780781646779721</v>
       </c>
       <c r="T42">
-        <v>0.7987642936667545</v>
+        <v>0.8089967885600022</v>
       </c>
       <c r="U42">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V42">
         <v>0.35</v>
       </c>
       <c r="W42">
-        <v>0.032695</v>
+        <v>0.03367</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y42">
-        <v>13.04631652008778</v>
+        <v>12.35953895772512</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1188708171600035</v>
+        <v>0.1184305978254326</v>
       </c>
       <c r="C43">
-        <v>20.89049251789393</v>
+        <v>20.65388045480427</v>
       </c>
       <c r="D43">
-        <v>28.10669251789394</v>
+        <v>28.17828045480427</v>
       </c>
       <c r="E43">
-        <v>11.7162</v>
+        <v>12.0244</v>
       </c>
       <c r="F43">
-        <v>12.6362</v>
+        <v>12.9444</v>
       </c>
       <c r="G43">
         <v>5.42</v>
@@ -4807,28 +4807,28 @@
         <v>8.09</v>
       </c>
       <c r="M43">
-        <v>0.65455516</v>
+        <v>0.67051992</v>
       </c>
       <c r="N43">
-        <v>7.43544484</v>
+        <v>7.41948008</v>
       </c>
       <c r="O43">
-        <v>2.602405694</v>
+        <v>2.596818028</v>
       </c>
       <c r="P43">
-        <v>4.833039146</v>
+        <v>4.822662052</v>
       </c>
       <c r="Q43">
-        <v>5.263039146</v>
+        <v>5.252662052</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1780781646779721</v>
+        <v>0.1798089617679872</v>
       </c>
       <c r="T43">
-        <v>0.8089967885600022</v>
+        <v>0.8195821281047413</v>
       </c>
       <c r="U43">
         <v>0.0518</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>12.35953895772512</v>
+        <v>12.06526422063643</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1184305978254326</v>
+        <v>0.1179903784908616</v>
       </c>
       <c r="C44">
-        <v>20.65388045480427</v>
+        <v>20.41763399282703</v>
       </c>
       <c r="D44">
-        <v>28.17828045480427</v>
+        <v>28.25023399282703</v>
       </c>
       <c r="E44">
-        <v>12.0244</v>
+        <v>12.3326</v>
       </c>
       <c r="F44">
-        <v>12.9444</v>
+        <v>13.2526</v>
       </c>
       <c r="G44">
         <v>5.42</v>
@@ -4889,28 +4889,28 @@
         <v>8.09</v>
       </c>
       <c r="M44">
-        <v>0.6705199199999999</v>
+        <v>0.68648468</v>
       </c>
       <c r="N44">
-        <v>7.41948008</v>
+        <v>7.40351532</v>
       </c>
       <c r="O44">
-        <v>2.596818028</v>
+        <v>2.591230362</v>
       </c>
       <c r="P44">
-        <v>4.822662052</v>
+        <v>4.812284958</v>
       </c>
       <c r="Q44">
-        <v>5.252662052</v>
+        <v>5.242284958</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1798089617679872</v>
+        <v>0.181600488580459</v>
       </c>
       <c r="T44">
-        <v>0.8195821281047413</v>
+        <v>0.8305388830721028</v>
       </c>
       <c r="U44">
         <v>0.0518</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>12.06526422063643</v>
+        <v>11.78467668062163</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1179903784908616</v>
+        <v>0.1175501591562907</v>
       </c>
       <c r="C45">
-        <v>20.41763399282703</v>
+        <v>20.18175593983111</v>
       </c>
       <c r="D45">
-        <v>28.25023399282703</v>
+        <v>28.32255593983112</v>
       </c>
       <c r="E45">
-        <v>12.3326</v>
+        <v>12.6408</v>
       </c>
       <c r="F45">
-        <v>13.2526</v>
+        <v>13.5608</v>
       </c>
       <c r="G45">
         <v>5.42</v>
@@ -4971,28 +4971,28 @@
         <v>8.09</v>
       </c>
       <c r="M45">
-        <v>0.68648468</v>
+        <v>0.70244944</v>
       </c>
       <c r="N45">
-        <v>7.40351532</v>
+        <v>7.38755056</v>
       </c>
       <c r="O45">
-        <v>2.591230362</v>
+        <v>2.585642696</v>
       </c>
       <c r="P45">
-        <v>4.812284958</v>
+        <v>4.801907864</v>
       </c>
       <c r="Q45">
-        <v>5.242284958</v>
+        <v>5.231907864</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.181600488580459</v>
+        <v>0.1834559984933762</v>
       </c>
       <c r="T45">
-        <v>0.8305388830721028</v>
+        <v>0.8418869507168699</v>
       </c>
       <c r="U45">
         <v>0.0518</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>11.78467668062163</v>
+        <v>11.51684311969841</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1175501591562907</v>
+        <v>0.1171099398217197</v>
       </c>
       <c r="C46">
-        <v>20.18175593983111</v>
+        <v>19.94624913251231</v>
       </c>
       <c r="D46">
-        <v>28.32255593983112</v>
+        <v>28.39524913251232</v>
       </c>
       <c r="E46">
-        <v>12.6408</v>
+        <v>12.949</v>
       </c>
       <c r="F46">
-        <v>13.5608</v>
+        <v>13.869</v>
       </c>
       <c r="G46">
         <v>5.42</v>
@@ -5053,28 +5053,28 @@
         <v>8.09</v>
       </c>
       <c r="M46">
-        <v>0.70244944</v>
+        <v>0.7184142</v>
       </c>
       <c r="N46">
-        <v>7.38755056</v>
+        <v>7.3715858</v>
       </c>
       <c r="O46">
-        <v>2.585642696</v>
+        <v>2.58005503</v>
       </c>
       <c r="P46">
-        <v>4.801907864</v>
+        <v>4.79153077</v>
       </c>
       <c r="Q46">
-        <v>5.231907864</v>
+        <v>5.221530769999999</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1834559984933762</v>
+        <v>0.1853789814940359</v>
       </c>
       <c r="T46">
-        <v>0.8418869507168699</v>
+        <v>0.8536476753669014</v>
       </c>
       <c r="U46">
         <v>0.0518</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>11.51684311969841</v>
+        <v>11.260913272594</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1171099398217197</v>
+        <v>0.1166697204871488</v>
       </c>
       <c r="C47">
-        <v>19.94624913251231</v>
+        <v>19.71111643676421</v>
       </c>
       <c r="D47">
-        <v>28.39524913251232</v>
+        <v>28.4683164367642</v>
       </c>
       <c r="E47">
-        <v>12.949</v>
+        <v>13.2572</v>
       </c>
       <c r="F47">
-        <v>13.869</v>
+        <v>14.1772</v>
       </c>
       <c r="G47">
         <v>5.42</v>
@@ -5135,28 +5135,28 @@
         <v>8.09</v>
       </c>
       <c r="M47">
-        <v>0.7184142</v>
+        <v>0.73437896</v>
       </c>
       <c r="N47">
-        <v>7.3715858</v>
+        <v>7.35562104</v>
       </c>
       <c r="O47">
-        <v>2.58005503</v>
+        <v>2.574467364</v>
       </c>
       <c r="P47">
-        <v>4.79153077</v>
+        <v>4.781153676000001</v>
       </c>
       <c r="Q47">
-        <v>5.221530769999999</v>
+        <v>5.211153676</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1853789814940359</v>
+        <v>0.1873731860873126</v>
       </c>
       <c r="T47">
-        <v>0.8536476753669014</v>
+        <v>0.8658439824113786</v>
       </c>
       <c r="U47">
         <v>0.0518</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>11.260913272594</v>
+        <v>11.0161108101463</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1166697204871488</v>
+        <v>0.1162295011525779</v>
       </c>
       <c r="C48">
-        <v>19.71111643676421</v>
+        <v>19.47636074805482</v>
       </c>
       <c r="D48">
-        <v>28.4683164367642</v>
+        <v>28.54176074805482</v>
       </c>
       <c r="E48">
-        <v>13.2572</v>
+        <v>13.5654</v>
       </c>
       <c r="F48">
-        <v>14.1772</v>
+        <v>14.4854</v>
       </c>
       <c r="G48">
         <v>5.42</v>
@@ -5217,28 +5217,28 @@
         <v>8.09</v>
       </c>
       <c r="M48">
-        <v>0.73437896</v>
+        <v>0.75034372</v>
       </c>
       <c r="N48">
-        <v>7.35562104</v>
+        <v>7.33965628</v>
       </c>
       <c r="O48">
-        <v>2.574467364</v>
+        <v>2.568879698</v>
       </c>
       <c r="P48">
-        <v>4.781153676000001</v>
+        <v>4.770776582</v>
       </c>
       <c r="Q48">
-        <v>5.211153676</v>
+        <v>5.200776582</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1873731860873126</v>
+        <v>0.1894426436841092</v>
       </c>
       <c r="T48">
-        <v>0.8658439824113786</v>
+        <v>0.878500527457534</v>
       </c>
       <c r="U48">
         <v>0.0518</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>11.0161108101463</v>
+        <v>10.78172547376021</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1162295011525779</v>
+        <v>0.1157892818180069</v>
       </c>
       <c r="C49">
-        <v>19.47636074805482</v>
+        <v>19.24198499180909</v>
       </c>
       <c r="D49">
-        <v>28.54176074805482</v>
+        <v>28.61558499180909</v>
       </c>
       <c r="E49">
-        <v>13.5654</v>
+        <v>13.8736</v>
       </c>
       <c r="F49">
-        <v>14.4854</v>
+        <v>14.7936</v>
       </c>
       <c r="G49">
         <v>5.42</v>
@@ -5299,28 +5299,28 @@
         <v>8.09</v>
       </c>
       <c r="M49">
-        <v>0.75034372</v>
+        <v>0.7663084800000001</v>
       </c>
       <c r="N49">
-        <v>7.33965628</v>
+        <v>7.32369152</v>
       </c>
       <c r="O49">
-        <v>2.568879698</v>
+        <v>2.563292032</v>
       </c>
       <c r="P49">
-        <v>4.770776582</v>
+        <v>4.760399488</v>
       </c>
       <c r="Q49">
-        <v>5.200776582</v>
+        <v>5.190399488</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1894426436841092</v>
+        <v>0.1915916958038595</v>
       </c>
       <c r="T49">
-        <v>0.878500527457534</v>
+        <v>0.8916438626977725</v>
       </c>
       <c r="U49">
         <v>0.0518</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>10.78172547376021</v>
+        <v>10.55710619305687</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1157892818180069</v>
+        <v>0.115349062483436</v>
       </c>
       <c r="C50">
-        <v>19.24198499180909</v>
+        <v>19.0079921237973</v>
       </c>
       <c r="D50">
-        <v>28.61558499180909</v>
+        <v>28.6897921237973</v>
       </c>
       <c r="E50">
-        <v>13.8736</v>
+        <v>14.1818</v>
       </c>
       <c r="F50">
-        <v>14.7936</v>
+        <v>15.1018</v>
       </c>
       <c r="G50">
         <v>5.42</v>
@@ -5381,28 +5381,28 @@
         <v>8.09</v>
       </c>
       <c r="M50">
-        <v>0.76630848</v>
+        <v>0.78227324</v>
       </c>
       <c r="N50">
-        <v>7.32369152</v>
+        <v>7.30772676</v>
       </c>
       <c r="O50">
-        <v>2.563292032</v>
+        <v>2.557704366</v>
       </c>
       <c r="P50">
-        <v>4.760399488</v>
+        <v>4.750022394</v>
       </c>
       <c r="Q50">
-        <v>5.190399488</v>
+        <v>5.180022394</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1915916958038595</v>
+        <v>0.1938250244773254</v>
       </c>
       <c r="T50">
-        <v>0.8916438626977725</v>
+        <v>0.9053026228493927</v>
       </c>
       <c r="U50">
         <v>0.0518</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>10.55710619305687</v>
+        <v>10.3416550462598</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.115349062483436</v>
+        <v>0.114908843148865</v>
       </c>
       <c r="C51">
-        <v>19.0079921237973</v>
+        <v>18.77438513052953</v>
       </c>
       <c r="D51">
-        <v>28.6897921237973</v>
+        <v>28.76438513052953</v>
       </c>
       <c r="E51">
-        <v>14.1818</v>
+        <v>14.49</v>
       </c>
       <c r="F51">
-        <v>15.1018</v>
+        <v>15.41</v>
       </c>
       <c r="G51">
         <v>5.42</v>
@@ -5463,28 +5463,28 @@
         <v>8.09</v>
       </c>
       <c r="M51">
-        <v>0.78227324</v>
+        <v>0.798238</v>
       </c>
       <c r="N51">
-        <v>7.30772676</v>
+        <v>7.291762</v>
       </c>
       <c r="O51">
-        <v>2.557704366</v>
+        <v>2.5521167</v>
       </c>
       <c r="P51">
-        <v>4.750022394</v>
+        <v>4.7396453</v>
       </c>
       <c r="Q51">
-        <v>5.180022394</v>
+        <v>5.1696453</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1938250244773254</v>
+        <v>0.1961476862977301</v>
       </c>
       <c r="T51">
-        <v>0.9053026228493927</v>
+        <v>0.9195077334070778</v>
       </c>
       <c r="U51">
         <v>0.0518</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>10.3416550462598</v>
+        <v>10.1348219453346</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.114908843148865</v>
+        <v>0.1144686238142941</v>
       </c>
       <c r="C52">
-        <v>18.77438513052953</v>
+        <v>18.54116702965636</v>
       </c>
       <c r="D52">
-        <v>28.76438513052953</v>
+        <v>28.83936702965637</v>
       </c>
       <c r="E52">
-        <v>14.49</v>
+        <v>14.7982</v>
       </c>
       <c r="F52">
-        <v>15.41</v>
+        <v>15.7182</v>
       </c>
       <c r="G52">
         <v>5.42</v>
@@ -5545,28 +5545,28 @@
         <v>8.09</v>
       </c>
       <c r="M52">
-        <v>0.798238</v>
+        <v>0.81420276</v>
       </c>
       <c r="N52">
-        <v>7.291762</v>
+        <v>7.27579724</v>
       </c>
       <c r="O52">
-        <v>2.5521167</v>
+        <v>2.546529034</v>
       </c>
       <c r="P52">
-        <v>4.7396453</v>
+        <v>4.729268206</v>
       </c>
       <c r="Q52">
-        <v>5.1696453</v>
+        <v>5.159268206</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1961476862977301</v>
+        <v>0.1985651506414165</v>
       </c>
       <c r="T52">
-        <v>0.9195077334070778</v>
+        <v>0.9342926443956888</v>
       </c>
       <c r="U52">
         <v>0.0518</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>10.1348219453346</v>
+        <v>9.93609994640647</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1144686238142941</v>
+        <v>0.1146030044797232</v>
       </c>
       <c r="C53">
-        <v>18.54116702965636</v>
+        <v>18.21003675307352</v>
       </c>
       <c r="D53">
-        <v>28.83936702965637</v>
+        <v>28.81643675307352</v>
       </c>
       <c r="E53">
-        <v>14.7982</v>
+        <v>15.1064</v>
       </c>
       <c r="F53">
-        <v>15.7182</v>
+        <v>16.0264</v>
       </c>
       <c r="G53">
         <v>5.42</v>
@@ -5627,45 +5627,45 @@
         <v>8.09</v>
       </c>
       <c r="M53">
-        <v>0.81420276</v>
+        <v>0.8574124000000001</v>
       </c>
       <c r="N53">
-        <v>7.27579724</v>
+        <v>7.2325876</v>
       </c>
       <c r="O53">
-        <v>2.546529034</v>
+        <v>2.53140566</v>
       </c>
       <c r="P53">
-        <v>4.729268206</v>
+        <v>4.70118194</v>
       </c>
       <c r="Q53">
-        <v>5.159268206</v>
+        <v>5.131181939999999</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1985651506414165</v>
+        <v>0.2010833426660899</v>
       </c>
       <c r="T53">
-        <v>0.9342926443956888</v>
+        <v>0.9496935933421587</v>
       </c>
       <c r="U53">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V53">
         <v>0.35</v>
       </c>
       <c r="W53">
-        <v>0.03367</v>
+        <v>0.034775</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y53">
-        <v>9.93609994640647</v>
+        <v>9.435366225167725</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1146030044797232</v>
+        <v>0.1141738351451522</v>
       </c>
       <c r="C54">
-        <v>18.21003675307352</v>
+        <v>17.97519685946876</v>
       </c>
       <c r="D54">
-        <v>28.81643675307352</v>
+        <v>28.88979685946876</v>
       </c>
       <c r="E54">
-        <v>15.1064</v>
+        <v>15.4146</v>
       </c>
       <c r="F54">
-        <v>16.0264</v>
+        <v>16.3346</v>
       </c>
       <c r="G54">
         <v>5.42</v>
@@ -5709,28 +5709,28 @@
         <v>8.09</v>
       </c>
       <c r="M54">
-        <v>0.8574124000000001</v>
+        <v>0.8739011000000001</v>
       </c>
       <c r="N54">
-        <v>7.2325876</v>
+        <v>7.2160989</v>
       </c>
       <c r="O54">
-        <v>2.53140566</v>
+        <v>2.525634615</v>
       </c>
       <c r="P54">
-        <v>4.70118194</v>
+        <v>4.690464285</v>
       </c>
       <c r="Q54">
-        <v>5.131181939999999</v>
+        <v>5.120464285</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2010833426660899</v>
+        <v>0.2037086917981962</v>
       </c>
       <c r="T54">
-        <v>0.9496935933421587</v>
+        <v>0.9657499018182656</v>
       </c>
       <c r="U54">
         <v>0.0535</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>9.435366225167725</v>
+        <v>9.257340447334371</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1141738351451522</v>
+        <v>0.1137446658105813</v>
       </c>
       <c r="C55">
-        <v>17.97519685946876</v>
+        <v>17.7407314355338</v>
       </c>
       <c r="D55">
-        <v>28.88979685946876</v>
+        <v>28.9635314355338</v>
       </c>
       <c r="E55">
-        <v>15.4146</v>
+        <v>15.7228</v>
       </c>
       <c r="F55">
-        <v>16.3346</v>
+        <v>16.6428</v>
       </c>
       <c r="G55">
         <v>5.42</v>
@@ -5791,28 +5791,28 @@
         <v>8.09</v>
       </c>
       <c r="M55">
-        <v>0.8739011000000001</v>
+        <v>0.8903898</v>
       </c>
       <c r="N55">
-        <v>7.2160989</v>
+        <v>7.1996102</v>
       </c>
       <c r="O55">
-        <v>2.525634615</v>
+        <v>2.51986357</v>
       </c>
       <c r="P55">
-        <v>4.690464285</v>
+        <v>4.67974663</v>
       </c>
       <c r="Q55">
-        <v>5.120464285</v>
+        <v>5.10974663</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2037086917981962</v>
+        <v>0.2064481865447419</v>
       </c>
       <c r="T55">
-        <v>0.9657499018182656</v>
+        <v>0.9825043106628988</v>
       </c>
       <c r="U55">
         <v>0.0535</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>9.257340447334371</v>
+        <v>9.08590821682818</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1137446658105813</v>
+        <v>0.1133154964760103</v>
       </c>
       <c r="C56">
-        <v>17.7407314355338</v>
+        <v>17.506643355849</v>
       </c>
       <c r="D56">
-        <v>28.9635314355338</v>
+        <v>29.037643355849</v>
       </c>
       <c r="E56">
-        <v>15.7228</v>
+        <v>16.031</v>
       </c>
       <c r="F56">
-        <v>16.6428</v>
+        <v>16.951</v>
       </c>
       <c r="G56">
         <v>5.42</v>
@@ -5873,28 +5873,28 @@
         <v>8.09</v>
       </c>
       <c r="M56">
-        <v>0.8903898</v>
+        <v>0.9068785</v>
       </c>
       <c r="N56">
-        <v>7.1996102</v>
+        <v>7.183121499999999</v>
       </c>
       <c r="O56">
-        <v>2.51986357</v>
+        <v>2.514092525</v>
       </c>
       <c r="P56">
-        <v>4.67974663</v>
+        <v>4.669028975</v>
       </c>
       <c r="Q56">
-        <v>5.10974663</v>
+        <v>5.099028975</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2064481865447419</v>
+        <v>0.2093094366133563</v>
       </c>
       <c r="T56">
-        <v>0.9825043106628988</v>
+        <v>1.000003359900627</v>
       </c>
       <c r="U56">
         <v>0.0535</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>9.08590821682818</v>
+        <v>8.920709885613121</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1133154964760103</v>
+        <v>0.1128863271414394</v>
       </c>
       <c r="C57">
-        <v>17.506643355849</v>
+        <v>17.27293552449212</v>
       </c>
       <c r="D57">
-        <v>29.037643355849</v>
+        <v>29.11213552449213</v>
       </c>
       <c r="E57">
-        <v>16.031</v>
+        <v>16.3392</v>
       </c>
       <c r="F57">
-        <v>16.951</v>
+        <v>17.2592</v>
       </c>
       <c r="G57">
         <v>5.42</v>
@@ -5955,28 +5955,28 @@
         <v>8.09</v>
       </c>
       <c r="M57">
-        <v>0.9068785</v>
+        <v>0.9233672000000002</v>
       </c>
       <c r="N57">
-        <v>7.183121499999999</v>
+        <v>7.166632799999999</v>
       </c>
       <c r="O57">
-        <v>2.514092525</v>
+        <v>2.50832148</v>
       </c>
       <c r="P57">
-        <v>4.669028975</v>
+        <v>4.658311319999999</v>
       </c>
       <c r="Q57">
-        <v>5.099028975</v>
+        <v>5.088311319999999</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2093094366133563</v>
+        <v>0.2123007435032713</v>
       </c>
       <c r="T57">
-        <v>1.000003359900627</v>
+        <v>1.018297820467343</v>
       </c>
       <c r="U57">
         <v>0.0535</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>8.920709885613121</v>
+        <v>8.761411494798601</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1128863271414394</v>
+        <v>0.1124571578068684</v>
       </c>
       <c r="C58">
-        <v>17.27293552449212</v>
+        <v>17.03961087541769</v>
       </c>
       <c r="D58">
-        <v>29.11213552449213</v>
+        <v>29.18701087541769</v>
       </c>
       <c r="E58">
-        <v>16.3392</v>
+        <v>16.6474</v>
       </c>
       <c r="F58">
-        <v>17.2592</v>
+        <v>17.5674</v>
       </c>
       <c r="G58">
         <v>5.42</v>
@@ -6037,28 +6037,28 @@
         <v>8.09</v>
       </c>
       <c r="M58">
-        <v>0.9233672000000002</v>
+        <v>0.9398559000000001</v>
       </c>
       <c r="N58">
-        <v>7.166632799999999</v>
+        <v>7.150144099999999</v>
       </c>
       <c r="O58">
-        <v>2.50832148</v>
+        <v>2.502550435</v>
       </c>
       <c r="P58">
-        <v>4.658311319999999</v>
+        <v>4.647593665</v>
       </c>
       <c r="Q58">
-        <v>5.088311319999999</v>
+        <v>5.077593664999999</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2123007435032713</v>
+        <v>0.2154311809462057</v>
       </c>
       <c r="T58">
-        <v>1.018297820467343</v>
+        <v>1.037443186176696</v>
       </c>
       <c r="U58">
         <v>0.0535</v>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>8.761411494798601</v>
+        <v>8.607702521205642</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1124571578068684</v>
+        <v>0.1120279884722975</v>
       </c>
       <c r="C59">
-        <v>17.03961087541769</v>
+        <v>16.80667237284211</v>
       </c>
       <c r="D59">
-        <v>29.18701087541769</v>
+        <v>29.26227237284211</v>
       </c>
       <c r="E59">
-        <v>16.6474</v>
+        <v>16.9556</v>
       </c>
       <c r="F59">
-        <v>17.5674</v>
+        <v>17.8756</v>
       </c>
       <c r="G59">
         <v>5.42</v>
@@ -6119,28 +6119,28 @@
         <v>8.09</v>
       </c>
       <c r="M59">
-        <v>0.9398559000000001</v>
+        <v>0.9563446000000001</v>
       </c>
       <c r="N59">
-        <v>7.150144099999999</v>
+        <v>7.133655399999999</v>
       </c>
       <c r="O59">
-        <v>2.502550435</v>
+        <v>2.496779389999999</v>
       </c>
       <c r="P59">
-        <v>4.647593665</v>
+        <v>4.63687601</v>
       </c>
       <c r="Q59">
-        <v>5.077593664999999</v>
+        <v>5.06687601</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2154311809462057</v>
+        <v>0.2187106868388036</v>
       </c>
       <c r="T59">
-        <v>1.037443186176696</v>
+        <v>1.057500235967447</v>
       </c>
       <c r="U59">
         <v>0.0535</v>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>8.607702521205642</v>
+        <v>8.459293857046925</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1120279884722975</v>
+        <v>0.1115988191377266</v>
       </c>
       <c r="C60">
-        <v>16.80667237284212</v>
+        <v>16.57412301163492</v>
       </c>
       <c r="D60">
-        <v>29.26227237284211</v>
+        <v>29.33792301163492</v>
       </c>
       <c r="E60">
-        <v>16.9556</v>
+        <v>17.2638</v>
       </c>
       <c r="F60">
-        <v>17.8756</v>
+        <v>18.1838</v>
       </c>
       <c r="G60">
         <v>5.42</v>
@@ -6201,28 +6201,28 @@
         <v>8.09</v>
       </c>
       <c r="M60">
-        <v>0.9563445999999999</v>
+        <v>0.9728332999999999</v>
       </c>
       <c r="N60">
-        <v>7.1336554</v>
+        <v>7.1171667</v>
       </c>
       <c r="O60">
-        <v>2.49677939</v>
+        <v>2.491008345</v>
       </c>
       <c r="P60">
-        <v>4.63687601</v>
+        <v>4.626158355</v>
       </c>
       <c r="Q60">
-        <v>5.06687601</v>
+        <v>5.056158355</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2187106868388035</v>
+        <v>0.2221501686286013</v>
       </c>
       <c r="T60">
-        <v>1.057500235967447</v>
+        <v>1.078535678430918</v>
       </c>
       <c r="U60">
         <v>0.0535</v>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>8.459293857046926</v>
+        <v>8.315915995063081</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1115988191377266</v>
+        <v>0.1111696498031556</v>
       </c>
       <c r="C61">
-        <v>16.57412301163492</v>
+        <v>16.34196581771601</v>
       </c>
       <c r="D61">
-        <v>29.33792301163492</v>
+        <v>29.41396581771601</v>
       </c>
       <c r="E61">
-        <v>17.2638</v>
+        <v>17.572</v>
       </c>
       <c r="F61">
-        <v>18.1838</v>
+        <v>18.492</v>
       </c>
       <c r="G61">
         <v>5.42</v>
@@ -6283,28 +6283,28 @@
         <v>8.09</v>
       </c>
       <c r="M61">
-        <v>0.9728332999999999</v>
+        <v>0.989322</v>
       </c>
       <c r="N61">
-        <v>7.1171667</v>
+        <v>7.100678</v>
       </c>
       <c r="O61">
-        <v>2.491008345</v>
+        <v>2.4852373</v>
       </c>
       <c r="P61">
-        <v>4.626158355</v>
+        <v>4.615440700000001</v>
       </c>
       <c r="Q61">
-        <v>5.056158355</v>
+        <v>5.0454407</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2221501686286013</v>
+        <v>0.225761624507889</v>
       </c>
       <c r="T61">
-        <v>1.078535678430918</v>
+        <v>1.100622893017563</v>
       </c>
       <c r="U61">
         <v>0.0535</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>8.315915995063081</v>
+        <v>8.177317395145362</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1111696498031556</v>
+        <v>0.1107404804685847</v>
       </c>
       <c r="C62">
-        <v>16.34196581771601</v>
+        <v>16.11020384845908</v>
       </c>
       <c r="D62">
-        <v>29.41396581771601</v>
+        <v>29.49040384845908</v>
       </c>
       <c r="E62">
-        <v>17.572</v>
+        <v>17.8802</v>
       </c>
       <c r="F62">
-        <v>18.492</v>
+        <v>18.8002</v>
       </c>
       <c r="G62">
         <v>5.42</v>
@@ -6365,28 +6365,28 @@
         <v>8.09</v>
       </c>
       <c r="M62">
-        <v>0.989322</v>
+        <v>1.0058107</v>
       </c>
       <c r="N62">
-        <v>7.100678</v>
+        <v>7.0841893</v>
       </c>
       <c r="O62">
-        <v>2.4852373</v>
+        <v>2.479466255</v>
       </c>
       <c r="P62">
-        <v>4.615440700000001</v>
+        <v>4.604723045</v>
       </c>
       <c r="Q62">
-        <v>5.0454407</v>
+        <v>5.034723045</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.225761624507889</v>
+        <v>0.2295582832527812</v>
       </c>
       <c r="T62">
-        <v>1.100622893017563</v>
+        <v>1.123842785275317</v>
       </c>
       <c r="U62">
         <v>0.0535</v>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>8.177317395145362</v>
+        <v>8.043263011618389</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1107404804685847</v>
+        <v>0.1103113111340137</v>
       </c>
       <c r="C63">
-        <v>16.11020384845908</v>
+        <v>15.87884019310144</v>
       </c>
       <c r="D63">
-        <v>29.49040384845908</v>
+        <v>29.56724019310143</v>
       </c>
       <c r="E63">
-        <v>17.8802</v>
+        <v>18.1884</v>
       </c>
       <c r="F63">
-        <v>18.8002</v>
+        <v>19.1084</v>
       </c>
       <c r="G63">
         <v>5.42</v>
@@ -6447,28 +6447,28 @@
         <v>8.09</v>
       </c>
       <c r="M63">
-        <v>1.0058107</v>
+        <v>1.0222994</v>
       </c>
       <c r="N63">
-        <v>7.0841893</v>
+        <v>7.0677006</v>
       </c>
       <c r="O63">
-        <v>2.479466255</v>
+        <v>2.47369521</v>
       </c>
       <c r="P63">
-        <v>4.604723045</v>
+        <v>4.59400539</v>
       </c>
       <c r="Q63">
-        <v>5.034723045</v>
+        <v>5.02400539</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2295582832527812</v>
+        <v>0.2335547661421414</v>
       </c>
       <c r="T63">
-        <v>1.123842785275317</v>
+        <v>1.148284777125585</v>
       </c>
       <c r="U63">
         <v>0.0535</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>8.043263011618389</v>
+        <v>7.9135329630439</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1103113111340137</v>
+        <v>0.1098821417994428</v>
       </c>
       <c r="C64">
-        <v>15.87884019310144</v>
+        <v>15.64787797316009</v>
       </c>
       <c r="D64">
-        <v>29.56724019310143</v>
+        <v>29.64447797316009</v>
       </c>
       <c r="E64">
-        <v>18.1884</v>
+        <v>18.4966</v>
       </c>
       <c r="F64">
-        <v>19.1084</v>
+        <v>19.4166</v>
       </c>
       <c r="G64">
         <v>5.42</v>
@@ -6529,28 +6529,28 @@
         <v>8.09</v>
       </c>
       <c r="M64">
-        <v>1.0222994</v>
+        <v>1.0387881</v>
       </c>
       <c r="N64">
-        <v>7.0677006</v>
+        <v>7.0512119</v>
       </c>
       <c r="O64">
-        <v>2.47369521</v>
+        <v>2.467924165</v>
       </c>
       <c r="P64">
-        <v>4.59400539</v>
+        <v>4.583287735000001</v>
       </c>
       <c r="Q64">
-        <v>5.02400539</v>
+        <v>5.013287735</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2335547661421414</v>
+        <v>0.2377672751336291</v>
       </c>
       <c r="T64">
-        <v>1.148284777125585</v>
+        <v>1.174047957724516</v>
       </c>
       <c r="U64">
         <v>0.0535</v>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>7.9135329630439</v>
+        <v>7.78792132870987</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1098821417994428</v>
+        <v>0.1094529724648718</v>
       </c>
       <c r="C65">
-        <v>15.64787797316009</v>
+        <v>15.41732034285457</v>
       </c>
       <c r="D65">
-        <v>29.64447797316009</v>
+        <v>29.72212034285457</v>
       </c>
       <c r="E65">
-        <v>18.4966</v>
+        <v>18.8048</v>
       </c>
       <c r="F65">
-        <v>19.4166</v>
+        <v>19.7248</v>
       </c>
       <c r="G65">
         <v>5.42</v>
@@ -6611,28 +6611,28 @@
         <v>8.09</v>
       </c>
       <c r="M65">
-        <v>1.0387881</v>
+        <v>1.0552768</v>
       </c>
       <c r="N65">
-        <v>7.0512119</v>
+        <v>7.0347232</v>
       </c>
       <c r="O65">
-        <v>2.467924165</v>
+        <v>2.46215312</v>
       </c>
       <c r="P65">
-        <v>4.583287735000001</v>
+        <v>4.57257008</v>
       </c>
       <c r="Q65">
-        <v>5.013287735</v>
+        <v>5.00257008</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2377672751336291</v>
+        <v>0.2422138124024218</v>
       </c>
       <c r="T65">
-        <v>1.174047957724516</v>
+        <v>1.201242426134499</v>
       </c>
       <c r="U65">
         <v>0.0535</v>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>7.78792132870987</v>
+        <v>7.666235057948777</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1094529724648718</v>
+        <v>0.1093618031303009</v>
       </c>
       <c r="C66">
-        <v>15.41732034285457</v>
+        <v>15.12566647800382</v>
       </c>
       <c r="D66">
-        <v>29.72212034285457</v>
+        <v>29.73866647800381</v>
       </c>
       <c r="E66">
-        <v>18.8048</v>
+        <v>19.113</v>
       </c>
       <c r="F66">
-        <v>19.7248</v>
+        <v>20.033</v>
       </c>
       <c r="G66">
         <v>5.42</v>
@@ -6693,45 +6693,45 @@
         <v>8.09</v>
       </c>
       <c r="M66">
-        <v>1.0552768</v>
+        <v>1.0877919</v>
       </c>
       <c r="N66">
-        <v>7.0347232</v>
+        <v>7.0022081</v>
       </c>
       <c r="O66">
-        <v>2.46215312</v>
+        <v>2.450772835</v>
       </c>
       <c r="P66">
-        <v>4.57257008</v>
+        <v>4.551435265</v>
       </c>
       <c r="Q66">
-        <v>5.00257008</v>
+        <v>4.981435265</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2422138124024218</v>
+        <v>0.2469144375151454</v>
       </c>
       <c r="T66">
-        <v>1.201242426134499</v>
+        <v>1.229990864167909</v>
       </c>
       <c r="U66">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V66">
         <v>0.35</v>
       </c>
       <c r="W66">
-        <v>0.034775</v>
+        <v>0.035295</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y66">
-        <v>7.666235057948777</v>
+        <v>7.437084243778612</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1093618031303009</v>
+        <v>0.1089378337957299</v>
       </c>
       <c r="C67">
-        <v>15.12566647800382</v>
+        <v>14.89465446223252</v>
       </c>
       <c r="D67">
-        <v>29.73866647800381</v>
+        <v>29.81585446223252</v>
       </c>
       <c r="E67">
-        <v>19.113</v>
+        <v>19.4212</v>
       </c>
       <c r="F67">
-        <v>20.033</v>
+        <v>20.3412</v>
       </c>
       <c r="G67">
         <v>5.42</v>
@@ -6775,28 +6775,28 @@
         <v>8.09</v>
       </c>
       <c r="M67">
-        <v>1.0877919</v>
+        <v>1.10452716</v>
       </c>
       <c r="N67">
-        <v>7.0022081</v>
+        <v>6.98547284</v>
       </c>
       <c r="O67">
-        <v>2.450772835</v>
+        <v>2.444915494</v>
       </c>
       <c r="P67">
-        <v>4.551435265</v>
+        <v>4.540557346</v>
       </c>
       <c r="Q67">
-        <v>4.981435265</v>
+        <v>4.970557346</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2469144375151454</v>
+        <v>0.251891569987441</v>
       </c>
       <c r="T67">
-        <v>1.229990864167909</v>
+        <v>1.26043038679152</v>
       </c>
       <c r="U67">
         <v>0.0543</v>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>7.437084243778612</v>
+        <v>7.324401149175906</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1089378337957299</v>
+        <v>0.108513864461159</v>
       </c>
       <c r="C68">
-        <v>14.89465446223252</v>
+        <v>14.66404417862104</v>
       </c>
       <c r="D68">
-        <v>29.81585446223252</v>
+        <v>29.89344417862104</v>
       </c>
       <c r="E68">
-        <v>19.4212</v>
+        <v>19.7294</v>
       </c>
       <c r="F68">
-        <v>20.3412</v>
+        <v>20.6494</v>
       </c>
       <c r="G68">
         <v>5.42</v>
@@ -6857,28 +6857,28 @@
         <v>8.09</v>
       </c>
       <c r="M68">
-        <v>1.10452716</v>
+        <v>1.12126242</v>
       </c>
       <c r="N68">
-        <v>6.98547284</v>
+        <v>6.96873758</v>
       </c>
       <c r="O68">
-        <v>2.444915494</v>
+        <v>2.439058153</v>
       </c>
       <c r="P68">
-        <v>4.540557346</v>
+        <v>4.529679427</v>
       </c>
       <c r="Q68">
-        <v>4.970557346</v>
+        <v>4.959679426999999</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.251891569987441</v>
+        <v>0.257170346851997</v>
       </c>
       <c r="T68">
-        <v>1.26043038679152</v>
+        <v>1.292714728968078</v>
       </c>
       <c r="U68">
         <v>0.0543</v>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>7.324401149175906</v>
+        <v>7.215081729038952</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.108513864461159</v>
+        <v>0.1080898951265881</v>
       </c>
       <c r="C69">
-        <v>14.66404417862104</v>
+        <v>14.4338387716317</v>
       </c>
       <c r="D69">
-        <v>29.89344417862104</v>
+        <v>29.9714387716317</v>
       </c>
       <c r="E69">
-        <v>19.7294</v>
+        <v>20.0376</v>
       </c>
       <c r="F69">
-        <v>20.6494</v>
+        <v>20.9576</v>
       </c>
       <c r="G69">
         <v>5.42</v>
@@ -6939,28 +6939,28 @@
         <v>8.09</v>
       </c>
       <c r="M69">
-        <v>1.12126242</v>
+        <v>1.13799768</v>
       </c>
       <c r="N69">
-        <v>6.96873758</v>
+        <v>6.95200232</v>
       </c>
       <c r="O69">
-        <v>2.439058153</v>
+        <v>2.433200812</v>
       </c>
       <c r="P69">
-        <v>4.529679427</v>
+        <v>4.518801508</v>
       </c>
       <c r="Q69">
-        <v>4.959679426999999</v>
+        <v>4.948801508</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.257170346851997</v>
+        <v>0.2627790472705878</v>
       </c>
       <c r="T69">
-        <v>1.292714728968078</v>
+        <v>1.327016842530669</v>
       </c>
       <c r="U69">
         <v>0.0543</v>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>7.215081729038952</v>
+        <v>7.108977585964849</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1080898951265881</v>
+        <v>0.1076659257920171</v>
       </c>
       <c r="C70">
-        <v>14.4338387716317</v>
+        <v>14.20404141862936</v>
       </c>
       <c r="D70">
-        <v>29.9714387716317</v>
+        <v>30.04984141862936</v>
       </c>
       <c r="E70">
-        <v>20.0376</v>
+        <v>20.3458</v>
       </c>
       <c r="F70">
-        <v>20.9576</v>
+        <v>21.2658</v>
       </c>
       <c r="G70">
         <v>5.42</v>
@@ -7021,28 +7021,28 @@
         <v>8.09</v>
       </c>
       <c r="M70">
-        <v>1.13799768</v>
+        <v>1.15473294</v>
       </c>
       <c r="N70">
-        <v>6.95200232</v>
+        <v>6.935267059999999</v>
       </c>
       <c r="O70">
-        <v>2.433200812</v>
+        <v>2.427343470999999</v>
       </c>
       <c r="P70">
-        <v>4.518801508</v>
+        <v>4.507923589</v>
       </c>
       <c r="Q70">
-        <v>4.948801508</v>
+        <v>4.937923589</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2627790472705878</v>
+        <v>0.2687495993290875</v>
       </c>
       <c r="T70">
-        <v>1.327016842530669</v>
+        <v>1.363531995677945</v>
       </c>
       <c r="U70">
         <v>0.0543</v>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>7.108977585964849</v>
+        <v>7.005948925298691</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1076659257920171</v>
+        <v>0.1072419564574462</v>
       </c>
       <c r="C71">
-        <v>14.20404141862936</v>
+        <v>13.97465533031292</v>
       </c>
       <c r="D71">
-        <v>30.04984141862936</v>
+        <v>30.12865533031292</v>
       </c>
       <c r="E71">
-        <v>20.3458</v>
+        <v>20.654</v>
       </c>
       <c r="F71">
-        <v>21.2658</v>
+        <v>21.574</v>
       </c>
       <c r="G71">
         <v>5.42</v>
@@ -7103,28 +7103,28 @@
         <v>8.09</v>
       </c>
       <c r="M71">
-        <v>1.15473294</v>
+        <v>1.1714682</v>
       </c>
       <c r="N71">
-        <v>6.935267059999999</v>
+        <v>6.9185318</v>
       </c>
       <c r="O71">
-        <v>2.427343470999999</v>
+        <v>2.42148613</v>
       </c>
       <c r="P71">
-        <v>4.507923589</v>
+        <v>4.49704567</v>
       </c>
       <c r="Q71">
-        <v>4.937923589</v>
+        <v>4.92704567</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2687495993290875</v>
+        <v>0.2751181881914873</v>
       </c>
       <c r="T71">
-        <v>1.363531995677945</v>
+        <v>1.402481492368371</v>
       </c>
       <c r="U71">
         <v>0.0543</v>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>7.005948925298691</v>
+        <v>6.905863940651568</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1072419564574462</v>
+        <v>0.1068179871228752</v>
       </c>
       <c r="C72">
-        <v>13.97465533031292</v>
+        <v>13.7456837511536</v>
       </c>
       <c r="D72">
-        <v>30.12865533031292</v>
+        <v>30.2078837511536</v>
       </c>
       <c r="E72">
-        <v>20.654</v>
+        <v>20.9622</v>
       </c>
       <c r="F72">
-        <v>21.574</v>
+        <v>21.8822</v>
       </c>
       <c r="G72">
         <v>5.42</v>
@@ -7185,28 +7185,28 @@
         <v>8.09</v>
       </c>
       <c r="M72">
-        <v>1.1714682</v>
+        <v>1.18820346</v>
       </c>
       <c r="N72">
-        <v>6.9185318</v>
+        <v>6.901796539999999</v>
       </c>
       <c r="O72">
-        <v>2.42148613</v>
+        <v>2.415628788999999</v>
       </c>
       <c r="P72">
-        <v>4.49704567</v>
+        <v>4.486167751</v>
       </c>
       <c r="Q72">
-        <v>4.92704567</v>
+        <v>4.916167751</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2751181881914873</v>
+        <v>0.2819259900788802</v>
       </c>
       <c r="T72">
-        <v>1.402481492368371</v>
+        <v>1.444117161244345</v>
       </c>
       <c r="U72">
         <v>0.0543</v>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>6.905863940651568</v>
+        <v>6.808598251346616</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1068179871228752</v>
+        <v>0.1063940177883043</v>
       </c>
       <c r="C73">
-        <v>13.74568375115361</v>
+        <v>13.51712995984014</v>
       </c>
       <c r="D73">
-        <v>30.2078837511536</v>
+        <v>30.28752995984014</v>
       </c>
       <c r="E73">
-        <v>20.9622</v>
+        <v>21.2704</v>
       </c>
       <c r="F73">
-        <v>21.8822</v>
+        <v>22.1904</v>
       </c>
       <c r="G73">
         <v>5.42</v>
@@ -7267,28 +7267,28 @@
         <v>8.09</v>
       </c>
       <c r="M73">
-        <v>1.18820346</v>
+        <v>1.20493872</v>
       </c>
       <c r="N73">
-        <v>6.901796539999999</v>
+        <v>6.88506128</v>
       </c>
       <c r="O73">
-        <v>2.415628788999999</v>
+        <v>2.409771448</v>
       </c>
       <c r="P73">
-        <v>4.486167751</v>
+        <v>4.475289832</v>
       </c>
       <c r="Q73">
-        <v>4.916167751</v>
+        <v>4.905289831999999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2819259900788801</v>
+        <v>0.2892200635296582</v>
       </c>
       <c r="T73">
-        <v>1.444117161244345</v>
+        <v>1.488726806468602</v>
       </c>
       <c r="U73">
         <v>0.0543</v>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>6.808598251346616</v>
+        <v>6.714034386744579</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1063940177883043</v>
+        <v>0.1059700484537333</v>
       </c>
       <c r="C74">
-        <v>13.51712995984014</v>
+        <v>13.28899726973111</v>
       </c>
       <c r="D74">
-        <v>30.28752995984014</v>
+        <v>30.36759726973111</v>
       </c>
       <c r="E74">
-        <v>21.2704</v>
+        <v>21.5786</v>
       </c>
       <c r="F74">
-        <v>22.1904</v>
+        <v>22.4986</v>
       </c>
       <c r="G74">
         <v>5.42</v>
@@ -7349,28 +7349,28 @@
         <v>8.09</v>
       </c>
       <c r="M74">
-        <v>1.20493872</v>
+        <v>1.22167398</v>
       </c>
       <c r="N74">
-        <v>6.88506128</v>
+        <v>6.86832602</v>
       </c>
       <c r="O74">
-        <v>2.409771448</v>
+        <v>2.403914107</v>
       </c>
       <c r="P74">
-        <v>4.475289832</v>
+        <v>4.464411912999999</v>
       </c>
       <c r="Q74">
-        <v>4.905289831999999</v>
+        <v>4.894411912999999</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2892200635296582</v>
+        <v>0.2970544387175309</v>
       </c>
       <c r="T74">
-        <v>1.488726806468602</v>
+        <v>1.536640869857619</v>
       </c>
       <c r="U74">
         <v>0.0543</v>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>6.714034386744579</v>
+        <v>6.622061312953559</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1059700484537333</v>
+        <v>0.1055460791191624</v>
       </c>
       <c r="C75">
-        <v>13.28899726973111</v>
+        <v>13.06128902931435</v>
       </c>
       <c r="D75">
-        <v>30.36759726973111</v>
+        <v>30.44808902931435</v>
       </c>
       <c r="E75">
-        <v>21.5786</v>
+        <v>21.8868</v>
       </c>
       <c r="F75">
-        <v>22.4986</v>
+        <v>22.8068</v>
       </c>
       <c r="G75">
         <v>5.42</v>
@@ -7431,28 +7431,28 @@
         <v>8.09</v>
       </c>
       <c r="M75">
-        <v>1.22167398</v>
+        <v>1.23840924</v>
       </c>
       <c r="N75">
-        <v>6.86832602</v>
+        <v>6.85159076</v>
       </c>
       <c r="O75">
-        <v>2.403914107</v>
+        <v>2.398056766</v>
       </c>
       <c r="P75">
-        <v>4.464411912999999</v>
+        <v>4.453533994</v>
       </c>
       <c r="Q75">
-        <v>4.894411912999999</v>
+        <v>4.883533994</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2970544387175309</v>
+        <v>0.3054914581506246</v>
       </c>
       <c r="T75">
-        <v>1.536640869857619</v>
+        <v>1.588240630430407</v>
       </c>
       <c r="U75">
         <v>0.0543</v>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>6.622061312953559</v>
+        <v>6.532573997913646</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1055460791191624</v>
+        <v>0.1051221097845915</v>
       </c>
       <c r="C76">
-        <v>13.06128902931435</v>
+        <v>12.83400862267381</v>
       </c>
       <c r="D76">
-        <v>30.44808902931435</v>
+        <v>30.52900862267381</v>
       </c>
       <c r="E76">
-        <v>21.8868</v>
+        <v>22.195</v>
       </c>
       <c r="F76">
-        <v>22.8068</v>
+        <v>23.115</v>
       </c>
       <c r="G76">
         <v>5.42</v>
@@ -7513,28 +7513,28 @@
         <v>8.09</v>
       </c>
       <c r="M76">
-        <v>1.23840924</v>
+        <v>1.2551445</v>
       </c>
       <c r="N76">
-        <v>6.85159076</v>
+        <v>6.8348555</v>
       </c>
       <c r="O76">
-        <v>2.398056766</v>
+        <v>2.392199425</v>
       </c>
       <c r="P76">
-        <v>4.453533994</v>
+        <v>4.442656075</v>
       </c>
       <c r="Q76">
-        <v>4.883533994</v>
+        <v>4.872656075</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.3054914581506246</v>
+        <v>0.3146034391383659</v>
       </c>
       <c r="T76">
-        <v>1.588240630430407</v>
+        <v>1.643968371849018</v>
       </c>
       <c r="U76">
         <v>0.0543</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>6.532573997913646</v>
+        <v>6.445473011274797</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1051221097845915</v>
+        <v>0.1046981404500205</v>
       </c>
       <c r="C77">
-        <v>12.83400862267381</v>
+        <v>12.60715946996384</v>
       </c>
       <c r="D77">
-        <v>30.52900862267381</v>
+        <v>30.61035946996384</v>
       </c>
       <c r="E77">
-        <v>22.195</v>
+        <v>22.5032</v>
       </c>
       <c r="F77">
-        <v>23.115</v>
+        <v>23.4232</v>
       </c>
       <c r="G77">
         <v>5.42</v>
@@ -7595,28 +7595,28 @@
         <v>8.09</v>
       </c>
       <c r="M77">
-        <v>1.2551445</v>
+        <v>1.27187976</v>
       </c>
       <c r="N77">
-        <v>6.8348555</v>
+        <v>6.81812024</v>
       </c>
       <c r="O77">
-        <v>2.392199425</v>
+        <v>2.386342084</v>
       </c>
       <c r="P77">
-        <v>4.442656075</v>
+        <v>4.431778156</v>
       </c>
       <c r="Q77">
-        <v>4.872656075</v>
+        <v>4.861778156</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3146034391383659</v>
+        <v>0.3244747518750856</v>
       </c>
       <c r="T77">
-        <v>1.643968371849018</v>
+        <v>1.70434009171918</v>
       </c>
       <c r="U77">
         <v>0.0543</v>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>6.445473011274797</v>
+        <v>6.360664155863287</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1046981404500205</v>
+        <v>0.1042741711154496</v>
       </c>
       <c r="C78">
-        <v>12.60715946996384</v>
+        <v>12.38074502789097</v>
       </c>
       <c r="D78">
-        <v>30.61035946996384</v>
+        <v>30.69214502789097</v>
       </c>
       <c r="E78">
-        <v>22.5032</v>
+        <v>22.8114</v>
       </c>
       <c r="F78">
-        <v>23.4232</v>
+        <v>23.7314</v>
       </c>
       <c r="G78">
         <v>5.42</v>
@@ -7677,28 +7677,28 @@
         <v>8.09</v>
       </c>
       <c r="M78">
-        <v>1.27187976</v>
+        <v>1.28861502</v>
       </c>
       <c r="N78">
-        <v>6.81812024</v>
+        <v>6.80138498</v>
       </c>
       <c r="O78">
-        <v>2.386342084</v>
+        <v>2.380484743</v>
       </c>
       <c r="P78">
-        <v>4.431778156</v>
+        <v>4.420900237</v>
       </c>
       <c r="Q78">
-        <v>4.861778156</v>
+        <v>4.850900236999999</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3244747518750856</v>
+        <v>0.3352044396323895</v>
       </c>
       <c r="T78">
-        <v>1.70434009171918</v>
+        <v>1.76996152636066</v>
       </c>
       <c r="U78">
         <v>0.0543</v>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>6.360664155863287</v>
+        <v>6.278058127865061</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1042741711154496</v>
+        <v>0.1038502017808786</v>
       </c>
       <c r="C79">
-        <v>12.38074502789097</v>
+        <v>12.15476879020358</v>
       </c>
       <c r="D79">
-        <v>30.69214502789097</v>
+        <v>30.77436879020358</v>
       </c>
       <c r="E79">
-        <v>22.8114</v>
+        <v>23.1196</v>
       </c>
       <c r="F79">
-        <v>23.7314</v>
+        <v>24.0396</v>
       </c>
       <c r="G79">
         <v>5.42</v>
@@ -7759,28 +7759,28 @@
         <v>8.09</v>
       </c>
       <c r="M79">
-        <v>1.28861502</v>
+        <v>1.30535028</v>
       </c>
       <c r="N79">
-        <v>6.80138498</v>
+        <v>6.78464972</v>
       </c>
       <c r="O79">
-        <v>2.380484743</v>
+        <v>2.374627402</v>
       </c>
       <c r="P79">
-        <v>4.420900237</v>
+        <v>4.410022318</v>
       </c>
       <c r="Q79">
-        <v>4.850900236999999</v>
+        <v>4.840022318</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3352044396323895</v>
+        <v>0.3469095535494484</v>
       </c>
       <c r="T79">
-        <v>1.76996152636066</v>
+        <v>1.841548545969547</v>
       </c>
       <c r="U79">
         <v>0.0543</v>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>6.278058127865061</v>
+        <v>6.197570203148843</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1038502017808786</v>
+        <v>0.1034262324463077</v>
       </c>
       <c r="C80">
-        <v>12.15476879020358</v>
+        <v>11.9292342881894</v>
       </c>
       <c r="D80">
-        <v>30.77436879020358</v>
+        <v>30.85703428818941</v>
       </c>
       <c r="E80">
-        <v>23.1196</v>
+        <v>23.4278</v>
       </c>
       <c r="F80">
-        <v>24.0396</v>
+        <v>24.3478</v>
       </c>
       <c r="G80">
         <v>5.42</v>
@@ -7841,28 +7841,28 @@
         <v>8.09</v>
       </c>
       <c r="M80">
-        <v>1.30535028</v>
+        <v>1.32208554</v>
       </c>
       <c r="N80">
-        <v>6.78464972</v>
+        <v>6.76791446</v>
       </c>
       <c r="O80">
-        <v>2.374627402</v>
+        <v>2.368770061</v>
       </c>
       <c r="P80">
-        <v>4.410022318</v>
+        <v>4.399144399000001</v>
       </c>
       <c r="Q80">
-        <v>4.840022318</v>
+        <v>4.829144399</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3469095535494484</v>
+        <v>0.3597294402205129</v>
       </c>
       <c r="T80">
-        <v>1.841548545969547</v>
+        <v>1.919953376969757</v>
       </c>
       <c r="U80">
         <v>0.0543</v>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>6.197570203148843</v>
+        <v>6.119119947412782</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1034262324463077</v>
+        <v>0.1035222631117367</v>
       </c>
       <c r="C81">
-        <v>11.9292342881894</v>
+        <v>11.60227135851388</v>
       </c>
       <c r="D81">
-        <v>30.85703428818941</v>
+        <v>30.83827135851388</v>
       </c>
       <c r="E81">
-        <v>23.4278</v>
+        <v>23.736</v>
       </c>
       <c r="F81">
-        <v>24.3478</v>
+        <v>24.656</v>
       </c>
       <c r="G81">
         <v>5.42</v>
@@ -7923,45 +7923,45 @@
         <v>8.09</v>
       </c>
       <c r="M81">
-        <v>1.32208554</v>
+        <v>1.3634768</v>
       </c>
       <c r="N81">
-        <v>6.76791446</v>
+        <v>6.7265232</v>
       </c>
       <c r="O81">
-        <v>2.368770061</v>
+        <v>2.35428312</v>
       </c>
       <c r="P81">
-        <v>4.399144399000001</v>
+        <v>4.37224008</v>
       </c>
       <c r="Q81">
-        <v>4.829144399</v>
+        <v>4.80224008</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3597294402205129</v>
+        <v>0.3738313155586838</v>
       </c>
       <c r="T81">
-        <v>1.919953376969757</v>
+        <v>2.006198691069988</v>
       </c>
       <c r="U81">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V81">
         <v>0.35</v>
       </c>
       <c r="W81">
-        <v>0.035295</v>
+        <v>0.035945</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y81">
-        <v>6.119119947412782</v>
+        <v>5.933360949009179</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1035222631117367</v>
+        <v>0.1031047937771658</v>
       </c>
       <c r="C82">
-        <v>11.60227135851388</v>
+        <v>11.3758049652976</v>
       </c>
       <c r="D82">
-        <v>30.83827135851388</v>
+        <v>30.9200049652976</v>
       </c>
       <c r="E82">
-        <v>23.736</v>
+        <v>24.0442</v>
       </c>
       <c r="F82">
-        <v>24.656</v>
+        <v>24.9642</v>
       </c>
       <c r="G82">
         <v>5.42</v>
@@ -8005,28 +8005,28 @@
         <v>8.09</v>
       </c>
       <c r="M82">
-        <v>1.3634768</v>
+        <v>1.38052026</v>
       </c>
       <c r="N82">
-        <v>6.7265232</v>
+        <v>6.70947974</v>
       </c>
       <c r="O82">
-        <v>2.35428312</v>
+        <v>2.348317909</v>
       </c>
       <c r="P82">
-        <v>4.37224008</v>
+        <v>4.361161831</v>
       </c>
       <c r="Q82">
-        <v>4.80224008</v>
+        <v>4.791161831</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3738313155586838</v>
+        <v>0.3894175988271886</v>
       </c>
       <c r="T82">
-        <v>2.006198691069988</v>
+        <v>2.101522459286033</v>
       </c>
       <c r="U82">
         <v>0.0553</v>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>5.933360949009179</v>
+        <v>5.860109579268325</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1031047937771658</v>
+        <v>0.1026873244425949</v>
       </c>
       <c r="C83">
-        <v>11.3758049652976</v>
+        <v>11.14977297614407</v>
       </c>
       <c r="D83">
-        <v>30.9200049652976</v>
+        <v>31.00217297614408</v>
       </c>
       <c r="E83">
-        <v>24.0442</v>
+        <v>24.3524</v>
       </c>
       <c r="F83">
-        <v>24.9642</v>
+        <v>25.2724</v>
       </c>
       <c r="G83">
         <v>5.42</v>
@@ -8087,28 +8087,28 @@
         <v>8.09</v>
       </c>
       <c r="M83">
-        <v>1.38052026</v>
+        <v>1.39756372</v>
       </c>
       <c r="N83">
-        <v>6.70947974</v>
+        <v>6.69243628</v>
       </c>
       <c r="O83">
-        <v>2.348317909</v>
+        <v>2.342352698</v>
       </c>
       <c r="P83">
-        <v>4.361161831</v>
+        <v>4.350083582</v>
       </c>
       <c r="Q83">
-        <v>4.791161831</v>
+        <v>4.780083582</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3894175988271886</v>
+        <v>0.4067356913477493</v>
       </c>
       <c r="T83">
-        <v>2.101522459286033</v>
+        <v>2.207437757303861</v>
       </c>
       <c r="U83">
         <v>0.0553</v>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>5.860109579268325</v>
+        <v>5.788644828301639</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1026873244425949</v>
+        <v>0.1022698551080239</v>
       </c>
       <c r="C84">
-        <v>11.14977297614407</v>
+        <v>10.92417886348731</v>
       </c>
       <c r="D84">
-        <v>31.00217297614408</v>
+        <v>31.08477886348731</v>
       </c>
       <c r="E84">
-        <v>24.3524</v>
+        <v>24.6606</v>
       </c>
       <c r="F84">
-        <v>25.2724</v>
+        <v>25.5806</v>
       </c>
       <c r="G84">
         <v>5.42</v>
@@ -8169,28 +8169,28 @@
         <v>8.09</v>
       </c>
       <c r="M84">
-        <v>1.39756372</v>
+        <v>1.41460718</v>
       </c>
       <c r="N84">
-        <v>6.69243628</v>
+        <v>6.67539282</v>
       </c>
       <c r="O84">
-        <v>2.342352698</v>
+        <v>2.336387487</v>
       </c>
       <c r="P84">
-        <v>4.350083582</v>
+        <v>4.339005333</v>
       </c>
       <c r="Q84">
-        <v>4.780083582</v>
+        <v>4.769005333</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.4067356913477493</v>
+        <v>0.426091206517788</v>
       </c>
       <c r="T84">
-        <v>2.207437757303861</v>
+        <v>2.325813678617904</v>
       </c>
       <c r="U84">
         <v>0.0553</v>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>5.788644828301639</v>
+        <v>5.71890211952692</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1022698551080239</v>
+        <v>0.101852385773453</v>
       </c>
       <c r="C85">
-        <v>10.92417886348731</v>
+        <v>10.69902613686961</v>
       </c>
       <c r="D85">
-        <v>31.08477886348731</v>
+        <v>31.16782613686962</v>
       </c>
       <c r="E85">
-        <v>24.6606</v>
+        <v>24.9688</v>
       </c>
       <c r="F85">
-        <v>25.5806</v>
+        <v>25.8888</v>
       </c>
       <c r="G85">
         <v>5.42</v>
@@ -8251,28 +8251,28 @@
         <v>8.09</v>
       </c>
       <c r="M85">
-        <v>1.41460718</v>
+        <v>1.43165064</v>
       </c>
       <c r="N85">
-        <v>6.67539282</v>
+        <v>6.65834936</v>
       </c>
       <c r="O85">
-        <v>2.336387487</v>
+        <v>2.330422276</v>
       </c>
       <c r="P85">
-        <v>4.339005333</v>
+        <v>4.327927084000001</v>
       </c>
       <c r="Q85">
-        <v>4.769005333</v>
+        <v>4.757927084</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.426091206517788</v>
+        <v>0.4478661610840814</v>
       </c>
       <c r="T85">
-        <v>2.325813678617904</v>
+        <v>2.458986590096202</v>
       </c>
       <c r="U85">
         <v>0.0553</v>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>5.71890211952692</v>
+        <v>5.650819951437313</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.101852385773453</v>
+        <v>0.1014349164388821</v>
       </c>
       <c r="C86">
-        <v>10.69902613686962</v>
+        <v>10.47431834343872</v>
       </c>
       <c r="D86">
-        <v>31.16782613686962</v>
+        <v>31.25131834343872</v>
       </c>
       <c r="E86">
-        <v>24.9688</v>
+        <v>25.277</v>
       </c>
       <c r="F86">
-        <v>25.8888</v>
+        <v>26.197</v>
       </c>
       <c r="G86">
         <v>5.42</v>
@@ -8333,28 +8333,28 @@
         <v>8.09</v>
       </c>
       <c r="M86">
-        <v>1.43165064</v>
+        <v>1.4486941</v>
       </c>
       <c r="N86">
-        <v>6.65834936</v>
+        <v>6.6413059</v>
       </c>
       <c r="O86">
-        <v>2.330422276</v>
+        <v>2.324457065</v>
       </c>
       <c r="P86">
-        <v>4.327927084000001</v>
+        <v>4.316848835</v>
       </c>
       <c r="Q86">
-        <v>4.757927084</v>
+        <v>4.746848835</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4478661610840811</v>
+        <v>0.4725444429258803</v>
       </c>
       <c r="T86">
-        <v>2.4589865900962</v>
+        <v>2.609915889771605</v>
       </c>
       <c r="U86">
         <v>0.0553</v>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>5.650819951437314</v>
+        <v>5.584339716714522</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1014349164388821</v>
+        <v>0.1010174471043111</v>
       </c>
       <c r="C87">
-        <v>10.47431834343872</v>
+        <v>10.25005906845275</v>
       </c>
       <c r="D87">
-        <v>31.25131834343872</v>
+        <v>31.33525906845275</v>
       </c>
       <c r="E87">
-        <v>25.277</v>
+        <v>25.5852</v>
       </c>
       <c r="F87">
-        <v>26.197</v>
+        <v>26.5052</v>
       </c>
       <c r="G87">
         <v>5.42</v>
@@ -8415,28 +8415,28 @@
         <v>8.09</v>
       </c>
       <c r="M87">
-        <v>1.4486941</v>
+        <v>1.46573756</v>
       </c>
       <c r="N87">
-        <v>6.6413059</v>
+        <v>6.62426244</v>
       </c>
       <c r="O87">
-        <v>2.324457065</v>
+        <v>2.318491854</v>
       </c>
       <c r="P87">
-        <v>4.316848835</v>
+        <v>4.305770586</v>
       </c>
       <c r="Q87">
-        <v>4.746848835</v>
+        <v>4.735770585999999</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4725444429258803</v>
+        <v>0.5007481936022221</v>
       </c>
       <c r="T87">
-        <v>2.609915889771605</v>
+        <v>2.782406517972067</v>
       </c>
       <c r="U87">
         <v>0.0553</v>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>5.584339716714522</v>
+        <v>5.519405533962028</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1010174471043111</v>
+        <v>0.1005999777697402</v>
       </c>
       <c r="C88">
-        <v>10.25005906845275</v>
+        <v>10.0262519357934</v>
       </c>
       <c r="D88">
-        <v>31.33525906845275</v>
+        <v>31.4196519357934</v>
       </c>
       <c r="E88">
-        <v>25.5852</v>
+        <v>25.8934</v>
       </c>
       <c r="F88">
-        <v>26.5052</v>
+        <v>26.8134</v>
       </c>
       <c r="G88">
         <v>5.42</v>
@@ -8497,28 +8497,28 @@
         <v>8.09</v>
       </c>
       <c r="M88">
-        <v>1.46573756</v>
+        <v>1.48278102</v>
       </c>
       <c r="N88">
-        <v>6.62426244</v>
+        <v>6.60721898</v>
       </c>
       <c r="O88">
-        <v>2.318491854</v>
+        <v>2.312526643</v>
       </c>
       <c r="P88">
-        <v>4.305770586</v>
+        <v>4.294692337</v>
       </c>
       <c r="Q88">
-        <v>4.735770585999999</v>
+        <v>4.724692337</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.5007481936022221</v>
+        <v>0.533290982844155</v>
       </c>
       <c r="T88">
-        <v>2.782406517972067</v>
+        <v>2.981434165895676</v>
       </c>
       <c r="U88">
         <v>0.0553</v>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>5.519405533962028</v>
+        <v>5.455964091042923</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1005999777697402</v>
+        <v>0.1001825084351692</v>
       </c>
       <c r="C89">
-        <v>10.0262519357934</v>
+        <v>9.802900608487569</v>
       </c>
       <c r="D89">
-        <v>31.4196519357934</v>
+        <v>31.50450060848757</v>
       </c>
       <c r="E89">
-        <v>25.8934</v>
+        <v>26.2016</v>
       </c>
       <c r="F89">
-        <v>26.8134</v>
+        <v>27.1216</v>
       </c>
       <c r="G89">
         <v>5.42</v>
@@ -8579,28 +8579,28 @@
         <v>8.09</v>
       </c>
       <c r="M89">
-        <v>1.48278102</v>
+        <v>1.49982448</v>
       </c>
       <c r="N89">
-        <v>6.60721898</v>
+        <v>6.59017552</v>
       </c>
       <c r="O89">
-        <v>2.312526643</v>
+        <v>2.306561432</v>
       </c>
       <c r="P89">
-        <v>4.294692337</v>
+        <v>4.283614088</v>
       </c>
       <c r="Q89">
-        <v>4.724692337</v>
+        <v>4.713614088</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.533290982844155</v>
+        <v>0.5712575702930768</v>
       </c>
       <c r="T89">
-        <v>2.981434165895676</v>
+        <v>3.213633088473222</v>
       </c>
       <c r="U89">
         <v>0.0553</v>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>5.455964091042923</v>
+        <v>5.393964499099255</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1001825084351692</v>
+        <v>0.09976503910059827</v>
       </c>
       <c r="C90">
-        <v>9.802900608487569</v>
+        <v>9.580008789237198</v>
       </c>
       <c r="D90">
-        <v>31.50450060848757</v>
+        <v>31.5898087892372</v>
       </c>
       <c r="E90">
-        <v>26.2016</v>
+        <v>26.5098</v>
       </c>
       <c r="F90">
-        <v>27.1216</v>
+        <v>27.4298</v>
       </c>
       <c r="G90">
         <v>5.42</v>
@@ -8661,28 +8661,28 @@
         <v>8.09</v>
       </c>
       <c r="M90">
-        <v>1.49982448</v>
+        <v>1.51686794</v>
       </c>
       <c r="N90">
-        <v>6.59017552</v>
+        <v>6.57313206</v>
       </c>
       <c r="O90">
-        <v>2.306561432</v>
+        <v>2.300596221</v>
       </c>
       <c r="P90">
-        <v>4.283614088</v>
+        <v>4.272535839</v>
       </c>
       <c r="Q90">
-        <v>4.713614088</v>
+        <v>4.702535838999999</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5712575702930768</v>
+        <v>0.6161271736418025</v>
       </c>
       <c r="T90">
-        <v>3.213633088473222</v>
+        <v>3.488049996973957</v>
       </c>
       <c r="U90">
         <v>0.0553</v>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>5.393964499099255</v>
+        <v>5.333358156412746</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.09976503910059827</v>
+        <v>0.09934756976602732</v>
       </c>
       <c r="C91">
-        <v>9.580008789237198</v>
+        <v>9.357580220957999</v>
       </c>
       <c r="D91">
-        <v>31.5898087892372</v>
+        <v>31.675580220958</v>
       </c>
       <c r="E91">
-        <v>26.5098</v>
+        <v>26.818</v>
       </c>
       <c r="F91">
-        <v>27.4298</v>
+        <v>27.738</v>
       </c>
       <c r="G91">
         <v>5.42</v>
@@ -8743,28 +8743,28 @@
         <v>8.09</v>
       </c>
       <c r="M91">
-        <v>1.51686794</v>
+        <v>1.5339114</v>
       </c>
       <c r="N91">
-        <v>6.57313206</v>
+        <v>6.5560886</v>
       </c>
       <c r="O91">
-        <v>2.300596221</v>
+        <v>2.29463101</v>
       </c>
       <c r="P91">
-        <v>4.272535839</v>
+        <v>4.26145759</v>
       </c>
       <c r="Q91">
-        <v>4.702535838999999</v>
+        <v>4.69145759</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.6161271736418025</v>
+        <v>0.6699706976602733</v>
       </c>
       <c r="T91">
-        <v>3.488049996973957</v>
+        <v>3.817350287174839</v>
       </c>
       <c r="U91">
         <v>0.0553</v>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>5.333358156412746</v>
+        <v>5.274098621341493</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.09934756976602732</v>
+        <v>0.09893010043145639</v>
       </c>
       <c r="C92">
-        <v>9.357580220957999</v>
+        <v>9.135618687326822</v>
       </c>
       <c r="D92">
-        <v>31.675580220958</v>
+        <v>31.76181868732683</v>
       </c>
       <c r="E92">
-        <v>26.818</v>
+        <v>27.1262</v>
       </c>
       <c r="F92">
-        <v>27.738</v>
+        <v>28.0462</v>
       </c>
       <c r="G92">
         <v>5.42</v>
@@ -8825,28 +8825,28 @@
         <v>8.09</v>
       </c>
       <c r="M92">
-        <v>1.5339114</v>
+        <v>1.55095486</v>
       </c>
       <c r="N92">
-        <v>6.5560886</v>
+        <v>6.53904514</v>
       </c>
       <c r="O92">
-        <v>2.29463101</v>
+        <v>2.288665799</v>
       </c>
       <c r="P92">
-        <v>4.26145759</v>
+        <v>4.250379341</v>
       </c>
       <c r="Q92">
-        <v>4.69145759</v>
+        <v>4.680379341</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6699706976602733</v>
+        <v>0.7357794492384045</v>
       </c>
       <c r="T92">
-        <v>3.817350287174839</v>
+        <v>4.219828419642584</v>
       </c>
       <c r="U92">
         <v>0.0553</v>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>5.274098621341493</v>
+        <v>5.216141493634443</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.09893010043145639</v>
+        <v>0.09851263109688546</v>
       </c>
       <c r="C93">
-        <v>9.135618687326822</v>
+        <v>8.914128013338097</v>
       </c>
       <c r="D93">
-        <v>31.76181868732683</v>
+        <v>31.8485280133381</v>
       </c>
       <c r="E93">
-        <v>27.1262</v>
+        <v>27.4344</v>
       </c>
       <c r="F93">
-        <v>28.0462</v>
+        <v>28.3544</v>
       </c>
       <c r="G93">
         <v>5.42</v>
@@ -8907,28 +8907,28 @@
         <v>8.09</v>
       </c>
       <c r="M93">
-        <v>1.55095486</v>
+        <v>1.56799832</v>
       </c>
       <c r="N93">
-        <v>6.53904514</v>
+        <v>6.52200168</v>
       </c>
       <c r="O93">
-        <v>2.288665799</v>
+        <v>2.282700588</v>
       </c>
       <c r="P93">
-        <v>4.250379341</v>
+        <v>4.239301092</v>
       </c>
       <c r="Q93">
-        <v>4.680379341</v>
+        <v>4.669301092</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.7357794492384045</v>
+        <v>0.8180403887110684</v>
       </c>
       <c r="T93">
-        <v>4.219828419642584</v>
+        <v>4.722926085227266</v>
       </c>
       <c r="U93">
         <v>0.0553</v>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>5.216141493634443</v>
+        <v>5.159444303486243</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.09851263109688546</v>
+        <v>0.0980951617623145</v>
       </c>
       <c r="C94">
-        <v>8.914128013338097</v>
+        <v>8.693112065869268</v>
       </c>
       <c r="D94">
-        <v>31.8485280133381</v>
+        <v>31.93571206586927</v>
       </c>
       <c r="E94">
-        <v>27.4344</v>
+        <v>27.7426</v>
       </c>
       <c r="F94">
-        <v>28.3544</v>
+        <v>28.6626</v>
       </c>
       <c r="G94">
         <v>5.42</v>
@@ -8989,28 +8989,28 @@
         <v>8.09</v>
       </c>
       <c r="M94">
-        <v>1.56799832</v>
+        <v>1.58504178</v>
       </c>
       <c r="N94">
-        <v>6.52200168</v>
+        <v>6.50495822</v>
       </c>
       <c r="O94">
-        <v>2.282700588</v>
+        <v>2.276735377</v>
       </c>
       <c r="P94">
-        <v>4.239301092</v>
+        <v>4.228222843</v>
       </c>
       <c r="Q94">
-        <v>4.669301092</v>
+        <v>4.658222843</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.8180403887110684</v>
+        <v>0.9238044537473505</v>
       </c>
       <c r="T94">
-        <v>4.722926085227266</v>
+        <v>5.369765940978999</v>
       </c>
       <c r="U94">
         <v>0.0553</v>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>5.159444303486243</v>
+        <v>5.103966407749832</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.0980951617623145</v>
+        <v>0.09767769242774357</v>
       </c>
       <c r="C95">
-        <v>8.693112065869268</v>
+        <v>8.472574754255721</v>
       </c>
       <c r="D95">
-        <v>31.93571206586927</v>
+        <v>32.02337475425572</v>
       </c>
       <c r="E95">
-        <v>27.7426</v>
+        <v>28.0508</v>
       </c>
       <c r="F95">
-        <v>28.6626</v>
+        <v>28.9708</v>
       </c>
       <c r="G95">
         <v>5.42</v>
@@ -9071,28 +9071,28 @@
         <v>8.09</v>
       </c>
       <c r="M95">
-        <v>1.58504178</v>
+        <v>1.60208524</v>
       </c>
       <c r="N95">
-        <v>6.50495822</v>
+        <v>6.48791476</v>
       </c>
       <c r="O95">
-        <v>2.276735377</v>
+        <v>2.270770166</v>
       </c>
       <c r="P95">
-        <v>4.228222843</v>
+        <v>4.217144594000001</v>
       </c>
       <c r="Q95">
-        <v>4.658222843</v>
+        <v>4.647144594</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.9238044537473505</v>
+        <v>1.06482320712906</v>
       </c>
       <c r="T95">
-        <v>5.369765940978999</v>
+        <v>6.232219081981311</v>
       </c>
       <c r="U95">
         <v>0.0553</v>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>5.103966407749832</v>
+        <v>5.04966889277377</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.09767769242774357</v>
+        <v>0.09726022309317263</v>
       </c>
       <c r="C96">
-        <v>8.472574754255721</v>
+        <v>8.252520030875068</v>
       </c>
       <c r="D96">
-        <v>32.02337475425572</v>
+        <v>32.11152003087507</v>
       </c>
       <c r="E96">
-        <v>28.0508</v>
+        <v>28.359</v>
       </c>
       <c r="F96">
-        <v>28.9708</v>
+        <v>29.279</v>
       </c>
       <c r="G96">
         <v>5.42</v>
@@ -9153,28 +9153,28 @@
         <v>8.09</v>
       </c>
       <c r="M96">
-        <v>1.60208524</v>
+        <v>1.6191287</v>
       </c>
       <c r="N96">
-        <v>6.48791476</v>
+        <v>6.4708713</v>
       </c>
       <c r="O96">
-        <v>2.270770166</v>
+        <v>2.264804955</v>
       </c>
       <c r="P96">
-        <v>4.217144594000001</v>
+        <v>4.206066345</v>
       </c>
       <c r="Q96">
-        <v>4.647144594</v>
+        <v>4.636066345</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.06482320712906</v>
+        <v>1.262249461863454</v>
       </c>
       <c r="T96">
-        <v>6.232219081981311</v>
+        <v>7.43965347938455</v>
       </c>
       <c r="U96">
         <v>0.0553</v>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>5.04966889277377</v>
+        <v>4.996514483376151</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.09726022309317263</v>
+        <v>0.09684275375860166</v>
       </c>
       <c r="C97">
-        <v>8.252520030875068</v>
+        <v>8.032951891741185</v>
       </c>
       <c r="D97">
-        <v>32.11152003087507</v>
+        <v>32.20015189174119</v>
       </c>
       <c r="E97">
-        <v>28.359</v>
+        <v>28.6672</v>
       </c>
       <c r="F97">
-        <v>29.279</v>
+        <v>29.5872</v>
       </c>
       <c r="G97">
         <v>5.42</v>
@@ -9235,28 +9235,28 @@
         <v>8.09</v>
       </c>
       <c r="M97">
-        <v>1.6191287</v>
+        <v>1.63617216</v>
       </c>
       <c r="N97">
-        <v>6.4708713</v>
+        <v>6.45382784</v>
       </c>
       <c r="O97">
-        <v>2.264804955</v>
+        <v>2.258839744</v>
       </c>
       <c r="P97">
-        <v>4.206066345</v>
+        <v>4.194988095999999</v>
       </c>
       <c r="Q97">
-        <v>4.636066345</v>
+        <v>4.624988095999999</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.262249461863454</v>
+        <v>1.558388843965044</v>
       </c>
       <c r="T97">
-        <v>7.43965347938455</v>
+        <v>9.250805075489405</v>
       </c>
       <c r="U97">
         <v>0.0553</v>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>4.996514483376151</v>
+        <v>4.944467457507649</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.09684275375860169</v>
+        <v>0.09642528442403075</v>
       </c>
       <c r="C98">
-        <v>8.032951891741181</v>
+        <v>7.813874377108046</v>
       </c>
       <c r="D98">
-        <v>32.20015189174118</v>
+        <v>32.28927437710804</v>
       </c>
       <c r="E98">
-        <v>28.6672</v>
+        <v>28.9754</v>
       </c>
       <c r="F98">
-        <v>29.5872</v>
+        <v>29.8954</v>
       </c>
       <c r="G98">
         <v>5.42</v>
@@ -9317,28 +9317,28 @@
         <v>8.09</v>
       </c>
       <c r="M98">
-        <v>1.63617216</v>
+        <v>1.65321562</v>
       </c>
       <c r="N98">
-        <v>6.45382784</v>
+        <v>6.43678438</v>
       </c>
       <c r="O98">
-        <v>2.258839744</v>
+        <v>2.252874533</v>
       </c>
       <c r="P98">
-        <v>4.194988095999999</v>
+        <v>4.183909847</v>
       </c>
       <c r="Q98">
-        <v>4.624988095999999</v>
+        <v>4.613909847</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.558388843965041</v>
+        <v>2.051954480801023</v>
       </c>
       <c r="T98">
-        <v>9.250805075489382</v>
+        <v>12.26939106899746</v>
       </c>
       <c r="U98">
         <v>0.0553</v>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>4.944467457507649</v>
+        <v>4.893493566193138</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.09642528442403075</v>
+        <v>0.0960078150894598</v>
       </c>
       <c r="C99">
-        <v>7.813874377108046</v>
+        <v>7.595291572083728</v>
       </c>
       <c r="D99">
-        <v>32.28927437710804</v>
+        <v>32.37889157208372</v>
       </c>
       <c r="E99">
-        <v>28.9754</v>
+        <v>29.2836</v>
       </c>
       <c r="F99">
-        <v>29.8954</v>
+        <v>30.2036</v>
       </c>
       <c r="G99">
         <v>5.42</v>
@@ -9399,28 +9399,28 @@
         <v>8.09</v>
       </c>
       <c r="M99">
-        <v>1.65321562</v>
+        <v>1.67025908</v>
       </c>
       <c r="N99">
-        <v>6.43678438</v>
+        <v>6.41974092</v>
       </c>
       <c r="O99">
-        <v>2.252874533</v>
+        <v>2.246909322</v>
       </c>
       <c r="P99">
-        <v>4.183909847</v>
+        <v>4.172831598</v>
       </c>
       <c r="Q99">
-        <v>4.613909847</v>
+        <v>4.602831598</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.051954480801023</v>
+        <v>3.039085754472987</v>
       </c>
       <c r="T99">
-        <v>12.26939106899746</v>
+        <v>18.30656305601363</v>
       </c>
       <c r="U99">
         <v>0.0553</v>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>4.893493566193138</v>
+        <v>4.843559958374841</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.0960078150894598</v>
+        <v>0.09559034575488885</v>
       </c>
       <c r="C100">
-        <v>7.595291572083728</v>
+        <v>7.377207607254491</v>
       </c>
       <c r="D100">
-        <v>32.37889157208372</v>
+        <v>32.46900760725449</v>
       </c>
       <c r="E100">
-        <v>29.2836</v>
+        <v>29.5918</v>
       </c>
       <c r="F100">
-        <v>30.2036</v>
+        <v>30.5118</v>
       </c>
       <c r="G100">
         <v>5.42</v>
@@ -9481,28 +9481,28 @@
         <v>8.09</v>
       </c>
       <c r="M100">
-        <v>1.67025908</v>
+        <v>1.68730254</v>
       </c>
       <c r="N100">
-        <v>6.41974092</v>
+        <v>6.40269746</v>
       </c>
       <c r="O100">
-        <v>2.246909322</v>
+        <v>2.240944111</v>
       </c>
       <c r="P100">
-        <v>4.172831598</v>
+        <v>4.161753349</v>
       </c>
       <c r="Q100">
-        <v>4.602831598</v>
+        <v>4.591753348999999</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.039085754472987</v>
+        <v>6.000479575488879</v>
       </c>
       <c r="T100">
-        <v>18.30656305601363</v>
+        <v>36.41807901706211</v>
       </c>
       <c r="U100">
         <v>0.0553</v>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>4.843559958374841</v>
+        <v>4.794635110310448</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.09559034575488885</v>
-      </c>
-      <c r="C101">
-        <v>7.377207607254491</v>
-      </c>
-      <c r="D101">
-        <v>32.46900760725449</v>
-      </c>
-      <c r="E101">
-        <v>29.5918</v>
-      </c>
-      <c r="F101">
-        <v>30.5118</v>
-      </c>
-      <c r="G101">
-        <v>5.42</v>
-      </c>
-      <c r="H101">
-        <v>29.9</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>8.52</v>
-      </c>
-      <c r="K101">
-        <v>0.4299999999999997</v>
-      </c>
-      <c r="L101">
-        <v>8.09</v>
-      </c>
-      <c r="M101">
-        <v>1.68730254</v>
-      </c>
-      <c r="N101">
-        <v>6.40269746</v>
-      </c>
-      <c r="O101">
-        <v>2.240944111</v>
-      </c>
-      <c r="P101">
-        <v>4.161753349</v>
-      </c>
-      <c r="Q101">
-        <v>4.591753348999999</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>6.000479575488879</v>
-      </c>
-      <c r="T101">
-        <v>36.41807901706211</v>
-      </c>
-      <c r="U101">
-        <v>0.0553</v>
-      </c>
-      <c r="V101">
-        <v>0.35</v>
-      </c>
-      <c r="W101">
-        <v>0.035945</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>A3/A-</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>4.794635110310448</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
